--- a/public/datos.xlsx
+++ b/public/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NicolasAcebo\OneDrive - LARTIRIGOYEN Y CIA. S.A\Escritorio\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D3184F-D985-46DE-AB02-FA1DD604AB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1757923C-9F75-4499-86D4-4D38D320E829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5F5C8F4A-A9C3-4394-B81C-80D194F2AEAA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="43">
   <si>
     <t>Precio de contado</t>
   </si>
@@ -107,9 +107,6 @@
     <t>CALDÉN</t>
   </si>
   <si>
-    <t>ICBC</t>
-  </si>
-  <si>
     <t>PROCAMPO</t>
   </si>
   <si>
@@ -153,6 +150,21 @@
   </si>
   <si>
     <t>Tipo de Empresa</t>
+  </si>
+  <si>
+    <t>Corralito</t>
+  </si>
+  <si>
+    <t>Macrigato</t>
+  </si>
+  <si>
+    <t>Queseio</t>
+  </si>
+  <si>
+    <t>infobae</t>
+  </si>
+  <si>
+    <t>euros</t>
   </si>
 </sst>
 </file>
@@ -538,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7F38534-621C-456A-88D0-E73BF73C904A}">
-  <dimension ref="A1:L132"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
@@ -546,7 +558,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -584,13 +596,13 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B2" s="1">
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -622,13 +634,13 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="1">
         <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -660,13 +672,13 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="1">
         <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -698,13 +710,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1">
         <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -736,13 +748,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1">
         <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
@@ -774,16 +786,16 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" s="1">
         <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>14</v>
@@ -812,13 +824,13 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" s="1">
         <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -850,13 +862,13 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1">
         <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
@@ -888,19 +900,19 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1">
         <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F10">
         <v>180</v>
@@ -926,13 +938,13 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1">
         <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -964,13 +976,13 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1">
         <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -979,7 +991,7 @@
         <v>14</v>
       </c>
       <c r="F12">
-        <v>270</v>
+        <v>314</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -1002,13 +1014,13 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" s="1">
         <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -1040,13 +1052,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" s="1">
         <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
@@ -1058,7 +1070,7 @@
         <v>360</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1078,13 +1090,13 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="1">
         <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -1116,13 +1128,13 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16" s="1">
         <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -1154,13 +1166,13 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="1">
         <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
@@ -1192,13 +1204,13 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="1">
         <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
@@ -1230,13 +1242,13 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" s="1">
         <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
@@ -1268,7 +1280,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="1">
         <v>100</v>
@@ -1306,7 +1318,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="1">
         <v>100</v>
@@ -1344,7 +1356,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="1">
         <v>100</v>
@@ -1382,7 +1394,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1">
         <v>100</v>
@@ -1420,7 +1432,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1">
         <v>100</v>
@@ -1458,7 +1470,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1">
         <v>100</v>
@@ -1496,7 +1508,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1">
         <v>100</v>
@@ -1534,7 +1546,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" s="1">
         <v>100</v>
@@ -1572,7 +1584,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" s="1">
         <v>100</v>
@@ -1610,7 +1622,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" s="1">
         <v>100</v>
@@ -1648,7 +1660,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" s="1">
         <v>100</v>
@@ -1686,7 +1698,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" s="1">
         <v>100</v>
@@ -1724,7 +1736,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="1">
         <v>100</v>
@@ -1762,13 +1774,13 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="1">
         <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -1800,13 +1812,13 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34" s="1">
         <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D34" t="s">
         <v>11</v>
@@ -1838,13 +1850,13 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B35" s="1">
         <v>100</v>
       </c>
       <c r="C35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
@@ -1876,13 +1888,13 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="1">
+        <v>100</v>
+      </c>
+      <c r="C36" t="s">
         <v>31</v>
-      </c>
-      <c r="B36" s="1">
-        <v>100</v>
-      </c>
-      <c r="C36" t="s">
-        <v>32</v>
       </c>
       <c r="D36" t="s">
         <v>11</v>
@@ -1914,13 +1926,13 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="1">
+        <v>100</v>
+      </c>
+      <c r="C37" t="s">
         <v>31</v>
-      </c>
-      <c r="B37" s="1">
-        <v>100</v>
-      </c>
-      <c r="C37" t="s">
-        <v>32</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
@@ -1952,13 +1964,13 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" s="1">
+        <v>100</v>
+      </c>
+      <c r="C38" t="s">
         <v>31</v>
-      </c>
-      <c r="B38" s="1">
-        <v>100</v>
-      </c>
-      <c r="C38" t="s">
-        <v>32</v>
       </c>
       <c r="D38" t="s">
         <v>11</v>
@@ -1990,7 +2002,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" s="1">
         <v>100</v>
@@ -2028,7 +2040,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B40" s="1">
         <v>100</v>
@@ -2066,7 +2078,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B41" s="1">
         <v>100</v>
@@ -2104,7 +2116,7 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B42" s="1">
         <v>100</v>
@@ -2142,7 +2154,7 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B43" s="1">
         <v>100</v>
@@ -2180,7 +2192,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B44" s="1">
         <v>100</v>
@@ -2218,7 +2230,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B45" s="1">
         <v>100</v>
@@ -2256,7 +2268,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B46" s="1">
         <v>100</v>
@@ -2294,7 +2306,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B47" s="1">
         <v>100</v>
@@ -2332,7 +2344,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B48" s="1">
         <v>100</v>
@@ -2370,7 +2382,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B49" s="1">
         <v>100</v>
@@ -2408,13 +2420,13 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B50" s="1">
         <v>100</v>
       </c>
       <c r="C50" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
@@ -2446,13 +2458,13 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B51" s="1">
         <v>100</v>
       </c>
       <c r="C51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
@@ -2484,13 +2496,13 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B52" s="1">
         <v>100</v>
       </c>
       <c r="C52" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
@@ -2522,13 +2534,13 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>34</v>
+      </c>
+      <c r="B53" s="1">
+        <v>100</v>
+      </c>
+      <c r="C53" t="s">
         <v>35</v>
-      </c>
-      <c r="B53" s="1">
-        <v>100</v>
-      </c>
-      <c r="C53" t="s">
-        <v>36</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
@@ -2560,13 +2572,13 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>34</v>
+      </c>
+      <c r="B54" s="1">
+        <v>100</v>
+      </c>
+      <c r="C54" t="s">
         <v>35</v>
-      </c>
-      <c r="B54" s="1">
-        <v>100</v>
-      </c>
-      <c r="C54" t="s">
-        <v>36</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
@@ -2598,13 +2610,13 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>34</v>
+      </c>
+      <c r="B55" s="1">
+        <v>100</v>
+      </c>
+      <c r="C55" t="s">
         <v>35</v>
-      </c>
-      <c r="B55" s="1">
-        <v>100</v>
-      </c>
-      <c r="C55" t="s">
-        <v>36</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
@@ -2636,13 +2648,13 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B56" s="1">
         <v>100</v>
       </c>
       <c r="C56" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
@@ -2674,13 +2686,13 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B57" s="1">
         <v>100</v>
       </c>
       <c r="C57" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -2712,13 +2724,13 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B58" s="1">
         <v>100</v>
       </c>
       <c r="C58" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
@@ -2750,7 +2762,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B59" s="1">
         <v>100</v>
@@ -2788,7 +2800,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B60" s="1">
         <v>100</v>
@@ -2826,7 +2838,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B61" s="1">
         <v>100</v>
@@ -2864,7 +2876,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B62" s="1">
         <v>100</v>
@@ -2902,7 +2914,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B63" s="1">
         <v>100</v>
@@ -2940,7 +2952,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B64" s="1">
         <v>100</v>
@@ -2978,13 +2990,13 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B65" s="1">
         <v>100</v>
       </c>
       <c r="C65" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -2993,7 +3005,7 @@
         <v>14</v>
       </c>
       <c r="F65">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G65" t="s">
         <v>16</v>
@@ -3002,27 +3014,27 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J65">
         <v>0</v>
       </c>
       <c r="K65" s="2">
-        <v>112.00000000000001</v>
+        <v>108</v>
       </c>
       <c r="L65" s="2">
-        <v>0.73000000000000065</v>
+        <v>0.32444444444444476</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B66" s="1">
         <v>100</v>
       </c>
       <c r="C66" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -3031,7 +3043,7 @@
         <v>14</v>
       </c>
       <c r="F66">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G66" t="s">
         <v>16</v>
@@ -3040,27 +3052,27 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J66">
         <v>0</v>
       </c>
       <c r="K66" s="2">
-        <v>117</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="L66" s="2">
-        <v>0.68944444444444419</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B67" s="1">
         <v>100</v>
       </c>
       <c r="C67" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -3069,7 +3081,7 @@
         <v>14</v>
       </c>
       <c r="F67">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G67" t="s">
         <v>16</v>
@@ -3078,27 +3090,27 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J67">
         <v>0</v>
       </c>
       <c r="K67" s="2">
-        <v>121</v>
+        <v>114.99999999999999</v>
       </c>
       <c r="L67" s="2">
-        <v>0.63874999999999982</v>
+        <v>0.36499999999999977</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B68" s="1">
         <v>100</v>
       </c>
       <c r="C68" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -3107,7 +3119,7 @@
         <v>14</v>
       </c>
       <c r="F68">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="G68" t="s">
         <v>16</v>
@@ -3116,27 +3128,27 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J68">
         <v>0</v>
       </c>
       <c r="K68" s="2">
-        <v>110.00000000000001</v>
+        <v>118</v>
       </c>
       <c r="L68" s="2">
-        <v>0.60833333333333384</v>
+        <v>0.36499999999999982</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B69" s="1">
         <v>100</v>
       </c>
       <c r="C69" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -3145,7 +3157,7 @@
         <v>14</v>
       </c>
       <c r="F69">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G69" t="s">
         <v>16</v>
@@ -3154,27 +3166,27 @@
         <v>0</v>
       </c>
       <c r="I69">
-        <v>14.000000000000002</v>
+        <v>6</v>
       </c>
       <c r="J69">
         <v>0</v>
       </c>
       <c r="K69" s="2">
-        <v>114.00000000000001</v>
+        <v>106</v>
       </c>
       <c r="L69" s="2">
-        <v>0.56777777777777827</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B70" s="1">
         <v>100</v>
       </c>
       <c r="C70" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
@@ -3183,7 +3195,7 @@
         <v>14</v>
       </c>
       <c r="F70">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G70" t="s">
         <v>16</v>
@@ -3192,27 +3204,27 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J70">
         <v>0</v>
       </c>
       <c r="K70" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="L70" s="2">
-        <v>0.54749999999999976</v>
+        <v>0.32444444444444476</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B71" s="1">
         <v>100</v>
       </c>
       <c r="C71" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -3221,7 +3233,7 @@
         <v>14</v>
       </c>
       <c r="F71">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G71" t="s">
         <v>16</v>
@@ -3230,27 +3242,27 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J71">
         <v>0</v>
       </c>
       <c r="K71" s="2">
-        <v>123</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="L71" s="2">
-        <v>0.55966666666666665</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B72" s="1">
         <v>100</v>
       </c>
       <c r="C72" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -3259,7 +3271,7 @@
         <v>14</v>
       </c>
       <c r="F72">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="G72" t="s">
         <v>16</v>
@@ -3268,27 +3280,27 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>28.000000000000004</v>
+        <v>15</v>
       </c>
       <c r="J72">
         <v>0</v>
       </c>
       <c r="K72" s="2">
-        <v>128</v>
+        <v>114.99999999999999</v>
       </c>
       <c r="L72" s="2">
-        <v>0.56777777777777783</v>
+        <v>0.36499999999999977</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B73" s="1">
         <v>100</v>
       </c>
       <c r="C73" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -3297,7 +3309,7 @@
         <v>14</v>
       </c>
       <c r="F73">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="G73" t="s">
         <v>16</v>
@@ -3306,27 +3318,27 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J73">
         <v>0</v>
       </c>
       <c r="K73" s="2">
-        <v>109.00000000000001</v>
+        <v>118</v>
       </c>
       <c r="L73" s="2">
-        <v>0.54750000000000054</v>
+        <v>0.36499999999999982</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B74" s="1">
         <v>100</v>
       </c>
       <c r="C74" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D74" t="s">
         <v>19</v>
@@ -3335,7 +3347,7 @@
         <v>14</v>
       </c>
       <c r="F74">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G74" t="s">
         <v>16</v>
@@ -3344,27 +3356,27 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J74">
         <v>0</v>
       </c>
       <c r="K74" s="2">
-        <v>112.00000000000001</v>
+        <v>106</v>
       </c>
       <c r="L74" s="2">
-        <v>0.48666666666666714</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B75" s="1">
         <v>100</v>
       </c>
       <c r="C75" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D75" t="s">
         <v>19</v>
@@ -3373,7 +3385,7 @@
         <v>14</v>
       </c>
       <c r="F75">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G75" t="s">
         <v>16</v>
@@ -3382,27 +3394,27 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J75">
         <v>0</v>
       </c>
       <c r="K75" s="2">
-        <v>115.99999999999999</v>
+        <v>108</v>
       </c>
       <c r="L75" s="2">
-        <v>0.48666666666666641</v>
+        <v>0.32444444444444476</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B76" s="1">
         <v>100</v>
       </c>
       <c r="C76" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D76" t="s">
         <v>19</v>
@@ -3411,7 +3423,7 @@
         <v>14</v>
       </c>
       <c r="F76">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G76" t="s">
         <v>16</v>
@@ -3420,27 +3432,27 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J76">
         <v>0</v>
       </c>
       <c r="K76" s="2">
-        <v>120</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="L76" s="2">
-        <v>0.48666666666666658</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B77" s="1">
         <v>100</v>
       </c>
       <c r="C77" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D77" t="s">
         <v>19</v>
@@ -3449,7 +3461,7 @@
         <v>14</v>
       </c>
       <c r="F77">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="G77" t="s">
         <v>16</v>
@@ -3458,27 +3470,27 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J77">
         <v>0</v>
       </c>
       <c r="K77" s="2">
-        <v>124</v>
+        <v>114.99999999999999</v>
       </c>
       <c r="L77" s="2">
-        <v>0.48666666666666664</v>
+        <v>0.36499999999999977</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B78" s="1">
         <v>100</v>
       </c>
       <c r="C78" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D78" t="s">
         <v>19</v>
@@ -3487,7 +3499,7 @@
         <v>14</v>
       </c>
       <c r="F78">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="G78" t="s">
         <v>16</v>
@@ -3496,27 +3508,27 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J78">
         <v>0</v>
       </c>
       <c r="K78" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="L78" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.36499999999999982</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B79" s="1">
         <v>100</v>
       </c>
       <c r="C79" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D79" t="s">
         <v>19</v>
@@ -3525,7 +3537,7 @@
         <v>14</v>
       </c>
       <c r="F79">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G79" t="s">
         <v>16</v>
@@ -3534,27 +3546,27 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J79">
         <v>0</v>
       </c>
       <c r="K79" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="L79" s="2">
-        <v>0.32444444444444476</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B80" s="1">
         <v>100</v>
       </c>
       <c r="C80" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D80" t="s">
         <v>19</v>
@@ -3563,7 +3575,7 @@
         <v>14</v>
       </c>
       <c r="F80">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G80" t="s">
         <v>16</v>
@@ -3572,27 +3584,27 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J80">
         <v>0</v>
       </c>
       <c r="K80" s="2">
-        <v>112.00000000000001</v>
+        <v>108</v>
       </c>
       <c r="L80" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.32444444444444476</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B81" s="1">
         <v>100</v>
       </c>
       <c r="C81" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D81" t="s">
         <v>19</v>
@@ -3601,7 +3613,7 @@
         <v>14</v>
       </c>
       <c r="F81">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G81" t="s">
         <v>16</v>
@@ -3610,27 +3622,27 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81" s="2">
-        <v>114.99999999999999</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="L81" s="2">
-        <v>0.36499999999999977</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B82" s="1">
         <v>100</v>
       </c>
       <c r="C82" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D82" t="s">
         <v>19</v>
@@ -3639,7 +3651,7 @@
         <v>14</v>
       </c>
       <c r="F82">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="G82" t="s">
         <v>16</v>
@@ -3648,27 +3660,27 @@
         <v>0</v>
       </c>
       <c r="I82">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J82">
         <v>0</v>
       </c>
       <c r="K82" s="2">
-        <v>118</v>
+        <v>114.99999999999999</v>
       </c>
       <c r="L82" s="2">
-        <v>0.36499999999999982</v>
+        <v>0.36499999999999977</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B83" s="1">
         <v>100</v>
       </c>
       <c r="C83" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D83" t="s">
         <v>19</v>
@@ -3677,7 +3689,7 @@
         <v>14</v>
       </c>
       <c r="F83">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="G83" t="s">
         <v>16</v>
@@ -3686,1877 +3698,775 @@
         <v>0</v>
       </c>
       <c r="I83">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J83">
         <v>0</v>
       </c>
       <c r="K83" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="L83" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.36499999999999982</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B84" s="1">
         <v>100</v>
       </c>
       <c r="C84" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D84" t="s">
         <v>19</v>
       </c>
       <c r="E84" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F84">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G84" t="s">
         <v>16</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>0.39137800925925947</v>
       </c>
       <c r="I84">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J84">
-        <v>0</v>
+        <v>6.4336111111111149</v>
       </c>
       <c r="K84" s="2">
-        <v>108</v>
+        <v>108.56228333333334</v>
       </c>
       <c r="L84" s="2">
-        <v>0.32444444444444476</v>
+        <v>0.520872236111111</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B85" s="1">
         <v>100</v>
       </c>
       <c r="C85" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D85" t="s">
         <v>19</v>
       </c>
       <c r="E85" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F85">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G85" t="s">
         <v>16</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>0.39760702340535009</v>
       </c>
       <c r="I85">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J85">
-        <v>0</v>
+        <v>9.804008796296305</v>
       </c>
       <c r="K85" s="2">
-        <v>112.00000000000001</v>
+        <v>112.00008897222223</v>
       </c>
       <c r="L85" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.48667027498456789</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B86" s="1">
         <v>100</v>
       </c>
       <c r="C86" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D86" t="s">
         <v>19</v>
       </c>
       <c r="E86" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F86">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G86" t="s">
         <v>16</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>0.41709773718002596</v>
       </c>
       <c r="I86">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J86">
-        <v>0</v>
+        <v>20.569203477371147</v>
       </c>
       <c r="K86" s="2">
-        <v>114.99999999999999</v>
+        <v>122.98058754691857</v>
       </c>
       <c r="L86" s="2">
-        <v>0.36499999999999977</v>
+        <v>0.46599524747918197</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B87" s="1">
         <v>100</v>
       </c>
       <c r="C87" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D87" t="s">
         <v>19</v>
       </c>
       <c r="E87" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F87">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="G87" t="s">
         <v>16</v>
       </c>
       <c r="H87">
-        <v>0</v>
+        <v>0.50397751875154939</v>
       </c>
       <c r="I87">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J87">
-        <v>0</v>
+        <v>37.280528784361188</v>
       </c>
       <c r="K87" s="2">
-        <v>118</v>
+        <v>140.0261393600484</v>
       </c>
       <c r="L87" s="2">
-        <v>0.36499999999999982</v>
+        <v>0.54109410616361719</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B88" s="1">
         <v>100</v>
       </c>
       <c r="C88" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D88" t="s">
         <v>19</v>
       </c>
       <c r="E88" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F88">
-        <v>60</v>
+        <v>360</v>
       </c>
       <c r="G88" t="s">
         <v>16</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>0.53303503052700441</v>
       </c>
       <c r="I88">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J88">
-        <v>0</v>
+        <v>52.573318079375774</v>
       </c>
       <c r="K88" s="2">
-        <v>106</v>
+        <v>155.62478444096328</v>
       </c>
       <c r="L88" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.56397350891532216</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B89" s="1">
         <v>100</v>
       </c>
       <c r="C89" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D89" t="s">
         <v>19</v>
       </c>
       <c r="E89" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F89">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G89" t="s">
         <v>16</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="I89">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J89">
-        <v>0</v>
+        <v>7.2328767123287676</v>
       </c>
       <c r="K89" s="2">
-        <v>108</v>
+        <v>109.37753424657535</v>
       </c>
       <c r="L89" s="2">
-        <v>0.32444444444444476</v>
+        <v>0.57046666666666701</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B90" s="1">
         <v>100</v>
       </c>
       <c r="C90" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D90" t="s">
         <v>19</v>
       </c>
       <c r="E90" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F90">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G90" t="s">
         <v>16</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="I90">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J90">
-        <v>0</v>
+        <v>10.849315068493151</v>
       </c>
       <c r="K90" s="2">
-        <v>112.00000000000001</v>
+        <v>113.06630136986303</v>
       </c>
       <c r="L90" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.52991111111111133</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B91" s="1">
         <v>100</v>
       </c>
       <c r="C91" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D91" t="s">
         <v>19</v>
       </c>
       <c r="E91" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F91">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G91" t="s">
         <v>16</v>
       </c>
       <c r="H91">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="I91">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J91">
-        <v>0</v>
+        <v>21.698630136986303</v>
       </c>
       <c r="K91" s="2">
-        <v>114.99999999999999</v>
+        <v>124.13260273972602</v>
       </c>
       <c r="L91" s="2">
-        <v>0.36499999999999977</v>
+        <v>0.48935555555555532</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B92" s="1">
         <v>100</v>
       </c>
       <c r="C92" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D92" t="s">
         <v>19</v>
       </c>
       <c r="E92" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F92">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="G92" t="s">
         <v>16</v>
       </c>
       <c r="H92">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="I92">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J92">
-        <v>0</v>
+        <v>32.547945205479458</v>
       </c>
       <c r="K92" s="2">
-        <v>118</v>
+        <v>135.19890410958905</v>
       </c>
       <c r="L92" s="2">
-        <v>0.36499999999999982</v>
+        <v>0.47583703703703728</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B93" s="1">
         <v>100</v>
       </c>
       <c r="C93" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D93" t="s">
         <v>19</v>
       </c>
       <c r="E93" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F93">
-        <v>60</v>
+        <v>360</v>
       </c>
       <c r="G93" t="s">
         <v>16</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="I93">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J93">
-        <v>0</v>
+        <v>43.397260273972606</v>
       </c>
       <c r="K93" s="2">
-        <v>106</v>
+        <v>146.26520547945205</v>
       </c>
       <c r="L93" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.46907777777777776</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B94" s="1">
         <v>100</v>
       </c>
       <c r="C94" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D94" t="s">
         <v>19</v>
       </c>
       <c r="E94" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F94">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G94" t="s">
         <v>16</v>
       </c>
       <c r="H94">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="I94">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J94">
-        <v>0</v>
+        <v>5.0958904109589049</v>
       </c>
       <c r="K94" s="2">
-        <v>108</v>
+        <v>107.19780821917809</v>
       </c>
       <c r="L94" s="2">
-        <v>0.32444444444444476</v>
+        <v>0.43786666666666657</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B95" s="1">
         <v>100</v>
       </c>
       <c r="C95" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D95" t="s">
         <v>19</v>
       </c>
       <c r="E95" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F95">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G95" t="s">
         <v>16</v>
       </c>
       <c r="H95">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="I95">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J95">
-        <v>0</v>
+        <v>7.6438356164383565</v>
       </c>
       <c r="K95" s="2">
-        <v>112.00000000000001</v>
+        <v>109.79671232876713</v>
       </c>
       <c r="L95" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.39731111111111145</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B96" s="1">
         <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D96" t="s">
         <v>19</v>
       </c>
       <c r="E96" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F96">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G96" t="s">
         <v>16</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="I96">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J96">
-        <v>0</v>
+        <v>15.287671232876713</v>
       </c>
       <c r="K96" s="2">
-        <v>114.99999999999999</v>
+        <v>117.59342465753424</v>
       </c>
       <c r="L96" s="2">
-        <v>0.36499999999999977</v>
+        <v>0.35675555555555544</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B97" s="1">
         <v>100</v>
       </c>
       <c r="C97" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D97" t="s">
         <v>19</v>
       </c>
       <c r="E97" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F97">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="G97" t="s">
         <v>16</v>
       </c>
       <c r="H97">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="I97">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J97">
-        <v>0</v>
+        <v>22.93150684931507</v>
       </c>
       <c r="K97" s="2">
-        <v>118</v>
+        <v>125.39013698630137</v>
       </c>
       <c r="L97" s="2">
-        <v>0.36499999999999982</v>
+        <v>0.34323703703703701</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B98" s="1">
         <v>100</v>
       </c>
       <c r="C98" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D98" t="s">
         <v>19</v>
       </c>
       <c r="E98" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F98">
-        <v>60</v>
+        <v>360</v>
       </c>
       <c r="G98" t="s">
         <v>16</v>
       </c>
       <c r="H98">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="I98">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J98">
-        <v>0</v>
+        <v>30.575342465753426</v>
       </c>
       <c r="K98" s="2">
-        <v>106</v>
+        <v>133.18684931506849</v>
       </c>
       <c r="L98" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.3364777777777776</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B99" s="1">
         <v>100</v>
       </c>
       <c r="C99" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D99" t="s">
         <v>19</v>
       </c>
       <c r="E99" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F99">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G99" t="s">
         <v>16</v>
       </c>
       <c r="H99">
-        <v>0</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="I99">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J99">
-        <v>0</v>
+        <v>6.9863013698630123</v>
       </c>
       <c r="K99" s="2">
-        <v>108</v>
+        <v>109.12602739726026</v>
       </c>
       <c r="L99" s="2">
-        <v>0.32444444444444476</v>
+        <v>0.55516666666666514</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B100" s="1">
         <v>100</v>
       </c>
       <c r="C100" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D100" t="s">
         <v>19</v>
       </c>
       <c r="E100" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F100">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G100" t="s">
         <v>16</v>
       </c>
       <c r="H100">
-        <v>0</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="I100">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J100">
-        <v>0</v>
+        <v>10.479452054794521</v>
       </c>
       <c r="K100" s="2">
-        <v>112.00000000000001</v>
+        <v>112.68904109589042</v>
       </c>
       <c r="L100" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.51461111111111146</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B101" s="1">
         <v>100</v>
       </c>
       <c r="C101" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D101" t="s">
         <v>19</v>
       </c>
       <c r="E101" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F101">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G101" t="s">
         <v>16</v>
       </c>
       <c r="H101">
-        <v>0</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="I101">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J101">
-        <v>0</v>
+        <v>20.958904109589042</v>
       </c>
       <c r="K101" s="2">
-        <v>114.99999999999999</v>
+        <v>123.37808219178083</v>
       </c>
       <c r="L101" s="2">
-        <v>0.36499999999999977</v>
+        <v>0.47405555555555584</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B102" s="1">
         <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D102" t="s">
         <v>19</v>
       </c>
       <c r="E102" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F102">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="G102" t="s">
         <v>16</v>
       </c>
       <c r="H102">
-        <v>0</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="I102">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J102">
-        <v>0</v>
+        <v>31.438356164383556</v>
       </c>
       <c r="K102" s="2">
-        <v>118</v>
+        <v>134.06712328767122</v>
       </c>
       <c r="L102" s="2">
-        <v>0.36499999999999982</v>
+        <v>0.46053703703703697</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B103" s="1">
         <v>100</v>
       </c>
       <c r="C103" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D103" t="s">
         <v>19</v>
       </c>
       <c r="E103" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F103">
-        <v>60</v>
+        <v>360</v>
       </c>
       <c r="G103" t="s">
         <v>16</v>
       </c>
       <c r="H103">
-        <v>0</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="I103">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J103">
-        <v>0</v>
+        <v>41.917808219178085</v>
       </c>
       <c r="K103" s="2">
-        <v>106</v>
+        <v>144.75616438356164</v>
       </c>
       <c r="L103" s="2">
-        <v>0.36500000000000032</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>33</v>
-      </c>
-      <c r="B104" s="1">
-        <v>100</v>
-      </c>
-      <c r="C104" t="s">
-        <v>25</v>
-      </c>
-      <c r="D104" t="s">
-        <v>19</v>
-      </c>
-      <c r="E104" t="s">
-        <v>14</v>
-      </c>
-      <c r="F104">
-        <v>90</v>
-      </c>
-      <c r="G104" t="s">
-        <v>16</v>
-      </c>
-      <c r="H104">
-        <v>0</v>
-      </c>
-      <c r="I104">
-        <v>8</v>
-      </c>
-      <c r="J104">
-        <v>0</v>
-      </c>
-      <c r="K104" s="2">
-        <v>108</v>
-      </c>
-      <c r="L104" s="2">
-        <v>0.32444444444444476</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>33</v>
-      </c>
-      <c r="B105" s="1">
-        <v>100</v>
-      </c>
-      <c r="C105" t="s">
-        <v>25</v>
-      </c>
-      <c r="D105" t="s">
-        <v>19</v>
-      </c>
-      <c r="E105" t="s">
-        <v>14</v>
-      </c>
-      <c r="F105">
-        <v>120</v>
-      </c>
-      <c r="G105" t="s">
-        <v>16</v>
-      </c>
-      <c r="H105">
-        <v>0</v>
-      </c>
-      <c r="I105">
-        <v>12</v>
-      </c>
-      <c r="J105">
-        <v>0</v>
-      </c>
-      <c r="K105" s="2">
-        <v>112.00000000000001</v>
-      </c>
-      <c r="L105" s="2">
-        <v>0.36500000000000032</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>33</v>
-      </c>
-      <c r="B106" s="1">
-        <v>100</v>
-      </c>
-      <c r="C106" t="s">
-        <v>25</v>
-      </c>
-      <c r="D106" t="s">
-        <v>19</v>
-      </c>
-      <c r="E106" t="s">
-        <v>14</v>
-      </c>
-      <c r="F106">
-        <v>150</v>
-      </c>
-      <c r="G106" t="s">
-        <v>16</v>
-      </c>
-      <c r="H106">
-        <v>0</v>
-      </c>
-      <c r="I106">
-        <v>15</v>
-      </c>
-      <c r="J106">
-        <v>0</v>
-      </c>
-      <c r="K106" s="2">
-        <v>114.99999999999999</v>
-      </c>
-      <c r="L106" s="2">
-        <v>0.36499999999999977</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>33</v>
-      </c>
-      <c r="B107" s="1">
-        <v>100</v>
-      </c>
-      <c r="C107" t="s">
-        <v>25</v>
-      </c>
-      <c r="D107" t="s">
-        <v>19</v>
-      </c>
-      <c r="E107" t="s">
-        <v>14</v>
-      </c>
-      <c r="F107">
-        <v>180</v>
-      </c>
-      <c r="G107" t="s">
-        <v>16</v>
-      </c>
-      <c r="H107">
-        <v>0</v>
-      </c>
-      <c r="I107">
-        <v>18</v>
-      </c>
-      <c r="J107">
-        <v>0</v>
-      </c>
-      <c r="K107" s="2">
-        <v>118</v>
-      </c>
-      <c r="L107" s="2">
-        <v>0.36499999999999982</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>33</v>
-      </c>
-      <c r="B108" s="1">
-        <v>100</v>
-      </c>
-      <c r="C108" t="s">
-        <v>26</v>
-      </c>
-      <c r="D108" t="s">
-        <v>19</v>
-      </c>
-      <c r="E108" t="s">
-        <v>14</v>
-      </c>
-      <c r="F108">
-        <v>60</v>
-      </c>
-      <c r="G108" t="s">
-        <v>16</v>
-      </c>
-      <c r="H108">
-        <v>0</v>
-      </c>
-      <c r="I108">
-        <v>6</v>
-      </c>
-      <c r="J108">
-        <v>0</v>
-      </c>
-      <c r="K108" s="2">
-        <v>106</v>
-      </c>
-      <c r="L108" s="2">
-        <v>0.36500000000000032</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>33</v>
-      </c>
-      <c r="B109" s="1">
-        <v>100</v>
-      </c>
-      <c r="C109" t="s">
-        <v>26</v>
-      </c>
-      <c r="D109" t="s">
-        <v>19</v>
-      </c>
-      <c r="E109" t="s">
-        <v>14</v>
-      </c>
-      <c r="F109">
-        <v>90</v>
-      </c>
-      <c r="G109" t="s">
-        <v>16</v>
-      </c>
-      <c r="H109">
-        <v>0</v>
-      </c>
-      <c r="I109">
-        <v>8</v>
-      </c>
-      <c r="J109">
-        <v>0</v>
-      </c>
-      <c r="K109" s="2">
-        <v>108</v>
-      </c>
-      <c r="L109" s="2">
-        <v>0.32444444444444476</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>33</v>
-      </c>
-      <c r="B110" s="1">
-        <v>100</v>
-      </c>
-      <c r="C110" t="s">
-        <v>26</v>
-      </c>
-      <c r="D110" t="s">
-        <v>19</v>
-      </c>
-      <c r="E110" t="s">
-        <v>14</v>
-      </c>
-      <c r="F110">
-        <v>120</v>
-      </c>
-      <c r="G110" t="s">
-        <v>16</v>
-      </c>
-      <c r="H110">
-        <v>0</v>
-      </c>
-      <c r="I110">
-        <v>12</v>
-      </c>
-      <c r="J110">
-        <v>0</v>
-      </c>
-      <c r="K110" s="2">
-        <v>112.00000000000001</v>
-      </c>
-      <c r="L110" s="2">
-        <v>0.36500000000000032</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>33</v>
-      </c>
-      <c r="B111" s="1">
-        <v>100</v>
-      </c>
-      <c r="C111" t="s">
-        <v>26</v>
-      </c>
-      <c r="D111" t="s">
-        <v>19</v>
-      </c>
-      <c r="E111" t="s">
-        <v>14</v>
-      </c>
-      <c r="F111">
-        <v>150</v>
-      </c>
-      <c r="G111" t="s">
-        <v>16</v>
-      </c>
-      <c r="H111">
-        <v>0</v>
-      </c>
-      <c r="I111">
-        <v>15</v>
-      </c>
-      <c r="J111">
-        <v>0</v>
-      </c>
-      <c r="K111" s="2">
-        <v>114.99999999999999</v>
-      </c>
-      <c r="L111" s="2">
-        <v>0.36499999999999977</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>33</v>
-      </c>
-      <c r="B112" s="1">
-        <v>100</v>
-      </c>
-      <c r="C112" t="s">
-        <v>26</v>
-      </c>
-      <c r="D112" t="s">
-        <v>19</v>
-      </c>
-      <c r="E112" t="s">
-        <v>14</v>
-      </c>
-      <c r="F112">
-        <v>180</v>
-      </c>
-      <c r="G112" t="s">
-        <v>16</v>
-      </c>
-      <c r="H112">
-        <v>0</v>
-      </c>
-      <c r="I112">
-        <v>18</v>
-      </c>
-      <c r="J112">
-        <v>0</v>
-      </c>
-      <c r="K112" s="2">
-        <v>118</v>
-      </c>
-      <c r="L112" s="2">
-        <v>0.36499999999999982</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>33</v>
-      </c>
-      <c r="B113" s="1">
-        <v>100</v>
-      </c>
-      <c r="C113" t="s">
-        <v>22</v>
-      </c>
-      <c r="D113" t="s">
-        <v>19</v>
-      </c>
-      <c r="E113" t="s">
-        <v>27</v>
-      </c>
-      <c r="F113">
-        <v>60</v>
-      </c>
-      <c r="G113" t="s">
-        <v>16</v>
-      </c>
-      <c r="H113">
-        <v>0.39137800925925947</v>
-      </c>
-      <c r="I113">
-        <v>2</v>
-      </c>
-      <c r="J113">
-        <v>6.4336111111111149</v>
-      </c>
-      <c r="K113" s="2">
-        <v>108.56228333333334</v>
-      </c>
-      <c r="L113" s="2">
-        <v>0.520872236111111</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>33</v>
-      </c>
-      <c r="B114" s="1">
-        <v>100</v>
-      </c>
-      <c r="C114" t="s">
-        <v>22</v>
-      </c>
-      <c r="D114" t="s">
-        <v>19</v>
-      </c>
-      <c r="E114" t="s">
-        <v>27</v>
-      </c>
-      <c r="F114">
-        <v>90</v>
-      </c>
-      <c r="G114" t="s">
-        <v>16</v>
-      </c>
-      <c r="H114">
-        <v>0.39760702340535009</v>
-      </c>
-      <c r="I114">
-        <v>2</v>
-      </c>
-      <c r="J114">
-        <v>9.804008796296305</v>
-      </c>
-      <c r="K114" s="2">
-        <v>112.00008897222223</v>
-      </c>
-      <c r="L114" s="2">
-        <v>0.48667027498456789</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>33</v>
-      </c>
-      <c r="B115" s="1">
-        <v>100</v>
-      </c>
-      <c r="C115" t="s">
-        <v>22</v>
-      </c>
-      <c r="D115" t="s">
-        <v>19</v>
-      </c>
-      <c r="E115" t="s">
-        <v>27</v>
-      </c>
-      <c r="F115">
-        <v>180</v>
-      </c>
-      <c r="G115" t="s">
-        <v>16</v>
-      </c>
-      <c r="H115">
-        <v>0.41709773718002596</v>
-      </c>
-      <c r="I115">
-        <v>2</v>
-      </c>
-      <c r="J115">
-        <v>20.569203477371147</v>
-      </c>
-      <c r="K115" s="2">
-        <v>122.98058754691857</v>
-      </c>
-      <c r="L115" s="2">
-        <v>0.46599524747918197</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>33</v>
-      </c>
-      <c r="B116" s="1">
-        <v>100</v>
-      </c>
-      <c r="C116" t="s">
-        <v>22</v>
-      </c>
-      <c r="D116" t="s">
-        <v>19</v>
-      </c>
-      <c r="E116" t="s">
-        <v>27</v>
-      </c>
-      <c r="F116">
-        <v>270</v>
-      </c>
-      <c r="G116" t="s">
-        <v>16</v>
-      </c>
-      <c r="H116">
-        <v>0.50397751875154939</v>
-      </c>
-      <c r="I116">
-        <v>2</v>
-      </c>
-      <c r="J116">
-        <v>37.280528784361188</v>
-      </c>
-      <c r="K116" s="2">
-        <v>140.0261393600484</v>
-      </c>
-      <c r="L116" s="2">
-        <v>0.54109410616361719</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>33</v>
-      </c>
-      <c r="B117" s="1">
-        <v>100</v>
-      </c>
-      <c r="C117" t="s">
-        <v>22</v>
-      </c>
-      <c r="D117" t="s">
-        <v>19</v>
-      </c>
-      <c r="E117" t="s">
-        <v>27</v>
-      </c>
-      <c r="F117">
-        <v>360</v>
-      </c>
-      <c r="G117" t="s">
-        <v>16</v>
-      </c>
-      <c r="H117">
-        <v>0.53303503052700441</v>
-      </c>
-      <c r="I117">
-        <v>2</v>
-      </c>
-      <c r="J117">
-        <v>52.573318079375774</v>
-      </c>
-      <c r="K117" s="2">
-        <v>155.62478444096328</v>
-      </c>
-      <c r="L117" s="2">
-        <v>0.56397350891532216</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>33</v>
-      </c>
-      <c r="B118" s="1">
-        <v>100</v>
-      </c>
-      <c r="C118" t="s">
-        <v>24</v>
-      </c>
-      <c r="D118" t="s">
-        <v>19</v>
-      </c>
-      <c r="E118" t="s">
-        <v>27</v>
-      </c>
-      <c r="F118">
-        <v>60</v>
-      </c>
-      <c r="G118" t="s">
-        <v>16</v>
-      </c>
-      <c r="H118">
-        <v>0.44</v>
-      </c>
-      <c r="I118">
-        <v>2</v>
-      </c>
-      <c r="J118">
-        <v>7.2328767123287676</v>
-      </c>
-      <c r="K118" s="2">
-        <v>109.37753424657535</v>
-      </c>
-      <c r="L118" s="2">
-        <v>0.57046666666666701</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>33</v>
-      </c>
-      <c r="B119" s="1">
-        <v>100</v>
-      </c>
-      <c r="C119" t="s">
-        <v>24</v>
-      </c>
-      <c r="D119" t="s">
-        <v>19</v>
-      </c>
-      <c r="E119" t="s">
-        <v>27</v>
-      </c>
-      <c r="F119">
-        <v>90</v>
-      </c>
-      <c r="G119" t="s">
-        <v>16</v>
-      </c>
-      <c r="H119">
-        <v>0.44</v>
-      </c>
-      <c r="I119">
-        <v>2</v>
-      </c>
-      <c r="J119">
-        <v>10.849315068493151</v>
-      </c>
-      <c r="K119" s="2">
-        <v>113.06630136986303</v>
-      </c>
-      <c r="L119" s="2">
-        <v>0.52991111111111133</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>33</v>
-      </c>
-      <c r="B120" s="1">
-        <v>100</v>
-      </c>
-      <c r="C120" t="s">
-        <v>24</v>
-      </c>
-      <c r="D120" t="s">
-        <v>19</v>
-      </c>
-      <c r="E120" t="s">
-        <v>27</v>
-      </c>
-      <c r="F120">
-        <v>180</v>
-      </c>
-      <c r="G120" t="s">
-        <v>16</v>
-      </c>
-      <c r="H120">
-        <v>0.44</v>
-      </c>
-      <c r="I120">
-        <v>2</v>
-      </c>
-      <c r="J120">
-        <v>21.698630136986303</v>
-      </c>
-      <c r="K120" s="2">
-        <v>124.13260273972602</v>
-      </c>
-      <c r="L120" s="2">
-        <v>0.48935555555555532</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>33</v>
-      </c>
-      <c r="B121" s="1">
-        <v>100</v>
-      </c>
-      <c r="C121" t="s">
-        <v>24</v>
-      </c>
-      <c r="D121" t="s">
-        <v>19</v>
-      </c>
-      <c r="E121" t="s">
-        <v>27</v>
-      </c>
-      <c r="F121">
-        <v>270</v>
-      </c>
-      <c r="G121" t="s">
-        <v>16</v>
-      </c>
-      <c r="H121">
-        <v>0.44</v>
-      </c>
-      <c r="I121">
-        <v>2</v>
-      </c>
-      <c r="J121">
-        <v>32.547945205479458</v>
-      </c>
-      <c r="K121" s="2">
-        <v>135.19890410958905</v>
-      </c>
-      <c r="L121" s="2">
-        <v>0.47583703703703728</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>33</v>
-      </c>
-      <c r="B122" s="1">
-        <v>100</v>
-      </c>
-      <c r="C122" t="s">
-        <v>24</v>
-      </c>
-      <c r="D122" t="s">
-        <v>19</v>
-      </c>
-      <c r="E122" t="s">
-        <v>27</v>
-      </c>
-      <c r="F122">
-        <v>360</v>
-      </c>
-      <c r="G122" t="s">
-        <v>16</v>
-      </c>
-      <c r="H122">
-        <v>0.44</v>
-      </c>
-      <c r="I122">
-        <v>2</v>
-      </c>
-      <c r="J122">
-        <v>43.397260273972606</v>
-      </c>
-      <c r="K122" s="2">
-        <v>146.26520547945205</v>
-      </c>
-      <c r="L122" s="2">
-        <v>0.46907777777777776</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>33</v>
-      </c>
-      <c r="B123" s="1">
-        <v>100</v>
-      </c>
-      <c r="C123" t="s">
-        <v>28</v>
-      </c>
-      <c r="D123" t="s">
-        <v>19</v>
-      </c>
-      <c r="E123" t="s">
-        <v>27</v>
-      </c>
-      <c r="F123">
-        <v>60</v>
-      </c>
-      <c r="G123" t="s">
-        <v>16</v>
-      </c>
-      <c r="H123">
-        <v>0.31</v>
-      </c>
-      <c r="I123">
-        <v>2</v>
-      </c>
-      <c r="J123">
-        <v>5.0958904109589049</v>
-      </c>
-      <c r="K123" s="2">
-        <v>107.19780821917809</v>
-      </c>
-      <c r="L123" s="2">
-        <v>0.43786666666666657</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>33</v>
-      </c>
-      <c r="B124" s="1">
-        <v>100</v>
-      </c>
-      <c r="C124" t="s">
-        <v>28</v>
-      </c>
-      <c r="D124" t="s">
-        <v>19</v>
-      </c>
-      <c r="E124" t="s">
-        <v>27</v>
-      </c>
-      <c r="F124">
-        <v>90</v>
-      </c>
-      <c r="G124" t="s">
-        <v>16</v>
-      </c>
-      <c r="H124">
-        <v>0.31</v>
-      </c>
-      <c r="I124">
-        <v>2</v>
-      </c>
-      <c r="J124">
-        <v>7.6438356164383565</v>
-      </c>
-      <c r="K124" s="2">
-        <v>109.79671232876713</v>
-      </c>
-      <c r="L124" s="2">
-        <v>0.39731111111111145</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>33</v>
-      </c>
-      <c r="B125" s="1">
-        <v>100</v>
-      </c>
-      <c r="C125" t="s">
-        <v>28</v>
-      </c>
-      <c r="D125" t="s">
-        <v>19</v>
-      </c>
-      <c r="E125" t="s">
-        <v>27</v>
-      </c>
-      <c r="F125">
-        <v>180</v>
-      </c>
-      <c r="G125" t="s">
-        <v>16</v>
-      </c>
-      <c r="H125">
-        <v>0.31</v>
-      </c>
-      <c r="I125">
-        <v>2</v>
-      </c>
-      <c r="J125">
-        <v>15.287671232876713</v>
-      </c>
-      <c r="K125" s="2">
-        <v>117.59342465753424</v>
-      </c>
-      <c r="L125" s="2">
-        <v>0.35675555555555544</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>33</v>
-      </c>
-      <c r="B126" s="1">
-        <v>100</v>
-      </c>
-      <c r="C126" t="s">
-        <v>28</v>
-      </c>
-      <c r="D126" t="s">
-        <v>19</v>
-      </c>
-      <c r="E126" t="s">
-        <v>27</v>
-      </c>
-      <c r="F126">
-        <v>270</v>
-      </c>
-      <c r="G126" t="s">
-        <v>16</v>
-      </c>
-      <c r="H126">
-        <v>0.31</v>
-      </c>
-      <c r="I126">
-        <v>2</v>
-      </c>
-      <c r="J126">
-        <v>22.93150684931507</v>
-      </c>
-      <c r="K126" s="2">
-        <v>125.39013698630137</v>
-      </c>
-      <c r="L126" s="2">
-        <v>0.34323703703703701</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>33</v>
-      </c>
-      <c r="B127" s="1">
-        <v>100</v>
-      </c>
-      <c r="C127" t="s">
-        <v>28</v>
-      </c>
-      <c r="D127" t="s">
-        <v>19</v>
-      </c>
-      <c r="E127" t="s">
-        <v>27</v>
-      </c>
-      <c r="F127">
-        <v>360</v>
-      </c>
-      <c r="G127" t="s">
-        <v>16</v>
-      </c>
-      <c r="H127">
-        <v>0.31</v>
-      </c>
-      <c r="I127">
-        <v>2</v>
-      </c>
-      <c r="J127">
-        <v>30.575342465753426</v>
-      </c>
-      <c r="K127" s="2">
-        <v>133.18684931506849</v>
-      </c>
-      <c r="L127" s="2">
-        <v>0.3364777777777776</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>33</v>
-      </c>
-      <c r="B128" s="1">
-        <v>100</v>
-      </c>
-      <c r="C128" t="s">
-        <v>29</v>
-      </c>
-      <c r="D128" t="s">
-        <v>19</v>
-      </c>
-      <c r="E128" t="s">
-        <v>27</v>
-      </c>
-      <c r="F128">
-        <v>60</v>
-      </c>
-      <c r="G128" t="s">
-        <v>16</v>
-      </c>
-      <c r="H128">
-        <v>0.42499999999999999</v>
-      </c>
-      <c r="I128">
-        <v>2</v>
-      </c>
-      <c r="J128">
-        <v>6.9863013698630123</v>
-      </c>
-      <c r="K128" s="2">
-        <v>109.12602739726026</v>
-      </c>
-      <c r="L128" s="2">
-        <v>0.55516666666666514</v>
-      </c>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>33</v>
-      </c>
-      <c r="B129" s="1">
-        <v>100</v>
-      </c>
-      <c r="C129" t="s">
-        <v>29</v>
-      </c>
-      <c r="D129" t="s">
-        <v>19</v>
-      </c>
-      <c r="E129" t="s">
-        <v>27</v>
-      </c>
-      <c r="F129">
-        <v>90</v>
-      </c>
-      <c r="G129" t="s">
-        <v>16</v>
-      </c>
-      <c r="H129">
-        <v>0.42499999999999999</v>
-      </c>
-      <c r="I129">
-        <v>2</v>
-      </c>
-      <c r="J129">
-        <v>10.479452054794521</v>
-      </c>
-      <c r="K129" s="2">
-        <v>112.68904109589042</v>
-      </c>
-      <c r="L129" s="2">
-        <v>0.51461111111111146</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>33</v>
-      </c>
-      <c r="B130" s="1">
-        <v>100</v>
-      </c>
-      <c r="C130" t="s">
-        <v>29</v>
-      </c>
-      <c r="D130" t="s">
-        <v>19</v>
-      </c>
-      <c r="E130" t="s">
-        <v>27</v>
-      </c>
-      <c r="F130">
-        <v>180</v>
-      </c>
-      <c r="G130" t="s">
-        <v>16</v>
-      </c>
-      <c r="H130">
-        <v>0.42499999999999999</v>
-      </c>
-      <c r="I130">
-        <v>2</v>
-      </c>
-      <c r="J130">
-        <v>20.958904109589042</v>
-      </c>
-      <c r="K130" s="2">
-        <v>123.37808219178083</v>
-      </c>
-      <c r="L130" s="2">
-        <v>0.47405555555555584</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>33</v>
-      </c>
-      <c r="B131" s="1">
-        <v>100</v>
-      </c>
-      <c r="C131" t="s">
-        <v>29</v>
-      </c>
-      <c r="D131" t="s">
-        <v>19</v>
-      </c>
-      <c r="E131" t="s">
-        <v>27</v>
-      </c>
-      <c r="F131">
-        <v>270</v>
-      </c>
-      <c r="G131" t="s">
-        <v>16</v>
-      </c>
-      <c r="H131">
-        <v>0.42499999999999999</v>
-      </c>
-      <c r="I131">
-        <v>2</v>
-      </c>
-      <c r="J131">
-        <v>31.438356164383556</v>
-      </c>
-      <c r="K131" s="2">
-        <v>134.06712328767122</v>
-      </c>
-      <c r="L131" s="2">
-        <v>0.46053703703703697</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>33</v>
-      </c>
-      <c r="B132" s="1">
-        <v>100</v>
-      </c>
-      <c r="C132" t="s">
-        <v>29</v>
-      </c>
-      <c r="D132" t="s">
-        <v>19</v>
-      </c>
-      <c r="E132" t="s">
-        <v>27</v>
-      </c>
-      <c r="F132">
-        <v>360</v>
-      </c>
-      <c r="G132" t="s">
-        <v>16</v>
-      </c>
-      <c r="H132">
-        <v>0.42499999999999999</v>
-      </c>
-      <c r="I132">
-        <v>2</v>
-      </c>
-      <c r="J132">
-        <v>41.917808219178085</v>
-      </c>
-      <c r="K132" s="2">
-        <v>144.75616438356164</v>
-      </c>
-      <c r="L132" s="2">
         <v>0.45377777777777778</v>
       </c>
     </row>

--- a/public/datos.xlsx
+++ b/public/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NicolasAcebo\OneDrive - LARTIRIGOYEN Y CIA. S.A\Escritorio\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1757923C-9F75-4499-86D4-4D38D320E829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D3184F-D985-46DE-AB02-FA1DD604AB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5F5C8F4A-A9C3-4394-B81C-80D194F2AEAA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="39">
   <si>
     <t>Precio de contado</t>
   </si>
@@ -107,6 +107,9 @@
     <t>CALDÉN</t>
   </si>
   <si>
+    <t>ICBC</t>
+  </si>
+  <si>
     <t>PROCAMPO</t>
   </si>
   <si>
@@ -150,21 +153,6 @@
   </si>
   <si>
     <t>Tipo de Empresa</t>
-  </si>
-  <si>
-    <t>Corralito</t>
-  </si>
-  <si>
-    <t>Macrigato</t>
-  </si>
-  <si>
-    <t>Queseio</t>
-  </si>
-  <si>
-    <t>infobae</t>
-  </si>
-  <si>
-    <t>euros</t>
   </si>
 </sst>
 </file>
@@ -550,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7F38534-621C-456A-88D0-E73BF73C904A}">
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L132"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
@@ -558,7 +546,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -596,13 +584,13 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1">
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -634,13 +622,13 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1">
         <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -672,13 +660,13 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" s="1">
         <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -710,13 +698,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" s="1">
         <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -748,13 +736,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1">
         <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
@@ -786,16 +774,16 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" s="1">
         <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>14</v>
@@ -824,13 +812,13 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1">
         <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -862,13 +850,13 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="1">
         <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
@@ -900,19 +888,19 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1">
         <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="F10">
         <v>180</v>
@@ -938,13 +926,13 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1">
         <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -976,13 +964,13 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1">
         <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -991,7 +979,7 @@
         <v>14</v>
       </c>
       <c r="F12">
-        <v>314</v>
+        <v>270</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -1014,13 +1002,13 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1">
         <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -1052,13 +1040,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="1">
         <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
@@ -1070,7 +1058,7 @@
         <v>360</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1090,13 +1078,13 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" s="1">
         <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -1128,13 +1116,13 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="1">
+        <v>100</v>
+      </c>
+      <c r="C16" t="s">
         <v>32</v>
-      </c>
-      <c r="B16" s="1">
-        <v>100</v>
-      </c>
-      <c r="C16" t="s">
-        <v>31</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -1166,13 +1154,13 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="1">
+        <v>100</v>
+      </c>
+      <c r="C17" t="s">
         <v>32</v>
-      </c>
-      <c r="B17" s="1">
-        <v>100</v>
-      </c>
-      <c r="C17" t="s">
-        <v>31</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
@@ -1204,13 +1192,13 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="1">
+        <v>100</v>
+      </c>
+      <c r="C18" t="s">
         <v>32</v>
-      </c>
-      <c r="B18" s="1">
-        <v>100</v>
-      </c>
-      <c r="C18" t="s">
-        <v>31</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
@@ -1242,13 +1230,13 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="1">
+        <v>100</v>
+      </c>
+      <c r="C19" t="s">
         <v>32</v>
-      </c>
-      <c r="B19" s="1">
-        <v>100</v>
-      </c>
-      <c r="C19" t="s">
-        <v>31</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
@@ -1280,7 +1268,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20" s="1">
         <v>100</v>
@@ -1318,7 +1306,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" s="1">
         <v>100</v>
@@ -1356,7 +1344,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B22" s="1">
         <v>100</v>
@@ -1394,7 +1382,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1">
         <v>100</v>
@@ -1432,7 +1420,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1">
         <v>100</v>
@@ -1470,7 +1458,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1">
         <v>100</v>
@@ -1508,7 +1496,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1">
         <v>100</v>
@@ -1546,7 +1534,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" s="1">
         <v>100</v>
@@ -1584,7 +1572,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28" s="1">
         <v>100</v>
@@ -1622,7 +1610,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B29" s="1">
         <v>100</v>
@@ -1660,7 +1648,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" s="1">
         <v>100</v>
@@ -1698,7 +1686,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" s="1">
         <v>100</v>
@@ -1736,7 +1724,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="1">
         <v>100</v>
@@ -1774,13 +1762,13 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B33" s="1">
         <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -1812,13 +1800,13 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B34" s="1">
         <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D34" t="s">
         <v>11</v>
@@ -1850,13 +1838,13 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B35" s="1">
         <v>100</v>
       </c>
       <c r="C35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
@@ -1888,13 +1876,13 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B36" s="1">
         <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D36" t="s">
         <v>11</v>
@@ -1926,13 +1914,13 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B37" s="1">
         <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
@@ -1964,13 +1952,13 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B38" s="1">
         <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D38" t="s">
         <v>11</v>
@@ -2002,7 +1990,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B39" s="1">
         <v>100</v>
@@ -2040,7 +2028,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B40" s="1">
         <v>100</v>
@@ -2078,7 +2066,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B41" s="1">
         <v>100</v>
@@ -2116,7 +2104,7 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B42" s="1">
         <v>100</v>
@@ -2154,7 +2142,7 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B43" s="1">
         <v>100</v>
@@ -2192,7 +2180,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B44" s="1">
         <v>100</v>
@@ -2230,7 +2218,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B45" s="1">
         <v>100</v>
@@ -2268,7 +2256,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B46" s="1">
         <v>100</v>
@@ -2306,7 +2294,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B47" s="1">
         <v>100</v>
@@ -2344,7 +2332,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B48" s="1">
         <v>100</v>
@@ -2382,7 +2370,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B49" s="1">
         <v>100</v>
@@ -2420,13 +2408,13 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>35</v>
+      </c>
+      <c r="B50" s="1">
+        <v>100</v>
+      </c>
+      <c r="C50" t="s">
         <v>34</v>
-      </c>
-      <c r="B50" s="1">
-        <v>100</v>
-      </c>
-      <c r="C50" t="s">
-        <v>33</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
@@ -2458,13 +2446,13 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" s="1">
+        <v>100</v>
+      </c>
+      <c r="C51" t="s">
         <v>34</v>
-      </c>
-      <c r="B51" s="1">
-        <v>100</v>
-      </c>
-      <c r="C51" t="s">
-        <v>33</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
@@ -2496,13 +2484,13 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>35</v>
+      </c>
+      <c r="B52" s="1">
+        <v>100</v>
+      </c>
+      <c r="C52" t="s">
         <v>34</v>
-      </c>
-      <c r="B52" s="1">
-        <v>100</v>
-      </c>
-      <c r="C52" t="s">
-        <v>33</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
@@ -2534,13 +2522,13 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B53" s="1">
         <v>100</v>
       </c>
       <c r="C53" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
@@ -2572,13 +2560,13 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B54" s="1">
         <v>100</v>
       </c>
       <c r="C54" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
@@ -2610,13 +2598,13 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B55" s="1">
         <v>100</v>
       </c>
       <c r="C55" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
@@ -2648,13 +2636,13 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B56" s="1">
         <v>100</v>
       </c>
       <c r="C56" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
@@ -2686,13 +2674,13 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B57" s="1">
         <v>100</v>
       </c>
       <c r="C57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -2724,13 +2712,13 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B58" s="1">
         <v>100</v>
       </c>
       <c r="C58" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
@@ -2762,7 +2750,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B59" s="1">
         <v>100</v>
@@ -2800,7 +2788,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B60" s="1">
         <v>100</v>
@@ -2838,7 +2826,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B61" s="1">
         <v>100</v>
@@ -2876,7 +2864,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B62" s="1">
         <v>100</v>
@@ -2914,7 +2902,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B63" s="1">
         <v>100</v>
@@ -2952,7 +2940,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B64" s="1">
         <v>100</v>
@@ -2990,13 +2978,13 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B65" s="1">
         <v>100</v>
       </c>
       <c r="C65" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -3005,7 +2993,7 @@
         <v>14</v>
       </c>
       <c r="F65">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G65" t="s">
         <v>16</v>
@@ -3014,27 +3002,27 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J65">
         <v>0</v>
       </c>
       <c r="K65" s="2">
-        <v>108</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="L65" s="2">
-        <v>0.32444444444444476</v>
+        <v>0.73000000000000065</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B66" s="1">
         <v>100</v>
       </c>
       <c r="C66" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -3043,7 +3031,7 @@
         <v>14</v>
       </c>
       <c r="F66">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G66" t="s">
         <v>16</v>
@@ -3052,27 +3040,27 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J66">
         <v>0</v>
       </c>
       <c r="K66" s="2">
-        <v>112.00000000000001</v>
+        <v>117</v>
       </c>
       <c r="L66" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.68944444444444419</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B67" s="1">
         <v>100</v>
       </c>
       <c r="C67" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -3081,7 +3069,7 @@
         <v>14</v>
       </c>
       <c r="F67">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G67" t="s">
         <v>16</v>
@@ -3090,27 +3078,27 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J67">
         <v>0</v>
       </c>
       <c r="K67" s="2">
-        <v>114.99999999999999</v>
+        <v>121</v>
       </c>
       <c r="L67" s="2">
-        <v>0.36499999999999977</v>
+        <v>0.63874999999999982</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B68" s="1">
         <v>100</v>
       </c>
       <c r="C68" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -3119,7 +3107,7 @@
         <v>14</v>
       </c>
       <c r="F68">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="G68" t="s">
         <v>16</v>
@@ -3128,27 +3116,27 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J68">
         <v>0</v>
       </c>
       <c r="K68" s="2">
-        <v>118</v>
+        <v>110.00000000000001</v>
       </c>
       <c r="L68" s="2">
-        <v>0.36499999999999982</v>
+        <v>0.60833333333333384</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B69" s="1">
         <v>100</v>
       </c>
       <c r="C69" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -3157,7 +3145,7 @@
         <v>14</v>
       </c>
       <c r="F69">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G69" t="s">
         <v>16</v>
@@ -3166,27 +3154,27 @@
         <v>0</v>
       </c>
       <c r="I69">
-        <v>6</v>
+        <v>14.000000000000002</v>
       </c>
       <c r="J69">
         <v>0</v>
       </c>
       <c r="K69" s="2">
-        <v>106</v>
+        <v>114.00000000000001</v>
       </c>
       <c r="L69" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.56777777777777827</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B70" s="1">
         <v>100</v>
       </c>
       <c r="C70" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
@@ -3195,7 +3183,7 @@
         <v>14</v>
       </c>
       <c r="F70">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G70" t="s">
         <v>16</v>
@@ -3204,27 +3192,27 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J70">
         <v>0</v>
       </c>
       <c r="K70" s="2">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="L70" s="2">
-        <v>0.32444444444444476</v>
+        <v>0.54749999999999976</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B71" s="1">
         <v>100</v>
       </c>
       <c r="C71" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -3233,7 +3221,7 @@
         <v>14</v>
       </c>
       <c r="F71">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G71" t="s">
         <v>16</v>
@@ -3242,27 +3230,27 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J71">
         <v>0</v>
       </c>
       <c r="K71" s="2">
-        <v>112.00000000000001</v>
+        <v>123</v>
       </c>
       <c r="L71" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.55966666666666665</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B72" s="1">
         <v>100</v>
       </c>
       <c r="C72" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -3271,7 +3259,7 @@
         <v>14</v>
       </c>
       <c r="F72">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G72" t="s">
         <v>16</v>
@@ -3280,27 +3268,27 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>15</v>
+        <v>28.000000000000004</v>
       </c>
       <c r="J72">
         <v>0</v>
       </c>
       <c r="K72" s="2">
-        <v>114.99999999999999</v>
+        <v>128</v>
       </c>
       <c r="L72" s="2">
-        <v>0.36499999999999977</v>
+        <v>0.56777777777777783</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B73" s="1">
         <v>100</v>
       </c>
       <c r="C73" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -3309,7 +3297,7 @@
         <v>14</v>
       </c>
       <c r="F73">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="G73" t="s">
         <v>16</v>
@@ -3318,27 +3306,27 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J73">
         <v>0</v>
       </c>
       <c r="K73" s="2">
-        <v>118</v>
+        <v>109.00000000000001</v>
       </c>
       <c r="L73" s="2">
-        <v>0.36499999999999982</v>
+        <v>0.54750000000000054</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B74" s="1">
         <v>100</v>
       </c>
       <c r="C74" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D74" t="s">
         <v>19</v>
@@ -3347,7 +3335,7 @@
         <v>14</v>
       </c>
       <c r="F74">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G74" t="s">
         <v>16</v>
@@ -3356,27 +3344,27 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J74">
         <v>0</v>
       </c>
       <c r="K74" s="2">
-        <v>106</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="L74" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.48666666666666714</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B75" s="1">
         <v>100</v>
       </c>
       <c r="C75" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D75" t="s">
         <v>19</v>
@@ -3385,7 +3373,7 @@
         <v>14</v>
       </c>
       <c r="F75">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G75" t="s">
         <v>16</v>
@@ -3394,27 +3382,27 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J75">
         <v>0</v>
       </c>
       <c r="K75" s="2">
-        <v>108</v>
+        <v>115.99999999999999</v>
       </c>
       <c r="L75" s="2">
-        <v>0.32444444444444476</v>
+        <v>0.48666666666666641</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B76" s="1">
         <v>100</v>
       </c>
       <c r="C76" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D76" t="s">
         <v>19</v>
@@ -3423,74 +3411,74 @@
         <v>14</v>
       </c>
       <c r="F76">
+        <v>150</v>
+      </c>
+      <c r="G76" t="s">
+        <v>16</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>20</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76" s="2">
         <v>120</v>
       </c>
-      <c r="G76" t="s">
-        <v>16</v>
-      </c>
-      <c r="H76">
-        <v>0</v>
-      </c>
-      <c r="I76">
-        <v>12</v>
-      </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-      <c r="K76" s="2">
-        <v>112.00000000000001</v>
-      </c>
       <c r="L76" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.48666666666666658</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B77" s="1">
         <v>100</v>
       </c>
       <c r="C77" t="s">
+        <v>21</v>
+      </c>
+      <c r="D77" t="s">
+        <v>19</v>
+      </c>
+      <c r="E77" t="s">
+        <v>14</v>
+      </c>
+      <c r="F77">
+        <v>180</v>
+      </c>
+      <c r="G77" t="s">
+        <v>16</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
         <v>24</v>
       </c>
-      <c r="D77" t="s">
-        <v>19</v>
-      </c>
-      <c r="E77" t="s">
-        <v>14</v>
-      </c>
-      <c r="F77">
-        <v>150</v>
-      </c>
-      <c r="G77" t="s">
-        <v>16</v>
-      </c>
-      <c r="H77">
-        <v>0</v>
-      </c>
-      <c r="I77">
-        <v>15</v>
-      </c>
       <c r="J77">
         <v>0</v>
       </c>
       <c r="K77" s="2">
-        <v>114.99999999999999</v>
+        <v>124</v>
       </c>
       <c r="L77" s="2">
-        <v>0.36499999999999977</v>
+        <v>0.48666666666666664</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B78" s="1">
         <v>100</v>
       </c>
       <c r="C78" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D78" t="s">
         <v>19</v>
@@ -3499,7 +3487,7 @@
         <v>14</v>
       </c>
       <c r="F78">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="G78" t="s">
         <v>16</v>
@@ -3508,27 +3496,27 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J78">
         <v>0</v>
       </c>
       <c r="K78" s="2">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="L78" s="2">
-        <v>0.36499999999999982</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B79" s="1">
         <v>100</v>
       </c>
       <c r="C79" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D79" t="s">
         <v>19</v>
@@ -3537,7 +3525,7 @@
         <v>14</v>
       </c>
       <c r="F79">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G79" t="s">
         <v>16</v>
@@ -3546,27 +3534,27 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J79">
         <v>0</v>
       </c>
       <c r="K79" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L79" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.32444444444444476</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B80" s="1">
         <v>100</v>
       </c>
       <c r="C80" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D80" t="s">
         <v>19</v>
@@ -3575,7 +3563,7 @@
         <v>14</v>
       </c>
       <c r="F80">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G80" t="s">
         <v>16</v>
@@ -3584,27 +3572,27 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J80">
         <v>0</v>
       </c>
       <c r="K80" s="2">
-        <v>108</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="L80" s="2">
-        <v>0.32444444444444476</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B81" s="1">
         <v>100</v>
       </c>
       <c r="C81" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D81" t="s">
         <v>19</v>
@@ -3613,7 +3601,7 @@
         <v>14</v>
       </c>
       <c r="F81">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G81" t="s">
         <v>16</v>
@@ -3622,27 +3610,27 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81" s="2">
-        <v>112.00000000000001</v>
+        <v>114.99999999999999</v>
       </c>
       <c r="L81" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.36499999999999977</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B82" s="1">
         <v>100</v>
       </c>
       <c r="C82" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D82" t="s">
         <v>19</v>
@@ -3651,7 +3639,7 @@
         <v>14</v>
       </c>
       <c r="F82">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G82" t="s">
         <v>16</v>
@@ -3660,27 +3648,27 @@
         <v>0</v>
       </c>
       <c r="I82">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J82">
         <v>0</v>
       </c>
       <c r="K82" s="2">
-        <v>114.99999999999999</v>
+        <v>118</v>
       </c>
       <c r="L82" s="2">
-        <v>0.36499999999999977</v>
+        <v>0.36499999999999982</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B83" s="1">
         <v>100</v>
       </c>
       <c r="C83" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D83" t="s">
         <v>19</v>
@@ -3689,7 +3677,7 @@
         <v>14</v>
       </c>
       <c r="F83">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="G83" t="s">
         <v>16</v>
@@ -3698,775 +3686,1877 @@
         <v>0</v>
       </c>
       <c r="I83">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J83">
         <v>0</v>
       </c>
       <c r="K83" s="2">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="L83" s="2">
-        <v>0.36499999999999982</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B84" s="1">
         <v>100</v>
       </c>
       <c r="C84" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D84" t="s">
         <v>19</v>
       </c>
       <c r="E84" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F84">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G84" t="s">
         <v>16</v>
       </c>
       <c r="H84">
-        <v>0.39137800925925947</v>
+        <v>0</v>
       </c>
       <c r="I84">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J84">
-        <v>6.4336111111111149</v>
+        <v>0</v>
       </c>
       <c r="K84" s="2">
-        <v>108.56228333333334</v>
+        <v>108</v>
       </c>
       <c r="L84" s="2">
-        <v>0.520872236111111</v>
+        <v>0.32444444444444476</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B85" s="1">
         <v>100</v>
       </c>
       <c r="C85" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D85" t="s">
         <v>19</v>
       </c>
       <c r="E85" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F85">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G85" t="s">
         <v>16</v>
       </c>
       <c r="H85">
-        <v>0.39760702340535009</v>
+        <v>0</v>
       </c>
       <c r="I85">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J85">
-        <v>9.804008796296305</v>
+        <v>0</v>
       </c>
       <c r="K85" s="2">
-        <v>112.00008897222223</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="L85" s="2">
-        <v>0.48667027498456789</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B86" s="1">
         <v>100</v>
       </c>
       <c r="C86" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D86" t="s">
         <v>19</v>
       </c>
       <c r="E86" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F86">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="G86" t="s">
         <v>16</v>
       </c>
       <c r="H86">
-        <v>0.41709773718002596</v>
+        <v>0</v>
       </c>
       <c r="I86">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J86">
-        <v>20.569203477371147</v>
+        <v>0</v>
       </c>
       <c r="K86" s="2">
-        <v>122.98058754691857</v>
+        <v>114.99999999999999</v>
       </c>
       <c r="L86" s="2">
-        <v>0.46599524747918197</v>
+        <v>0.36499999999999977</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B87" s="1">
         <v>100</v>
       </c>
       <c r="C87" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D87" t="s">
         <v>19</v>
       </c>
       <c r="E87" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F87">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="G87" t="s">
         <v>16</v>
       </c>
       <c r="H87">
-        <v>0.50397751875154939</v>
+        <v>0</v>
       </c>
       <c r="I87">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J87">
-        <v>37.280528784361188</v>
+        <v>0</v>
       </c>
       <c r="K87" s="2">
-        <v>140.0261393600484</v>
+        <v>118</v>
       </c>
       <c r="L87" s="2">
-        <v>0.54109410616361719</v>
+        <v>0.36499999999999982</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B88" s="1">
         <v>100</v>
       </c>
       <c r="C88" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D88" t="s">
         <v>19</v>
       </c>
       <c r="E88" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F88">
-        <v>360</v>
+        <v>60</v>
       </c>
       <c r="G88" t="s">
         <v>16</v>
       </c>
       <c r="H88">
-        <v>0.53303503052700441</v>
+        <v>0</v>
       </c>
       <c r="I88">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J88">
-        <v>52.573318079375774</v>
+        <v>0</v>
       </c>
       <c r="K88" s="2">
-        <v>155.62478444096328</v>
+        <v>106</v>
       </c>
       <c r="L88" s="2">
-        <v>0.56397350891532216</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B89" s="1">
         <v>100</v>
       </c>
       <c r="C89" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D89" t="s">
         <v>19</v>
       </c>
       <c r="E89" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F89">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G89" t="s">
         <v>16</v>
       </c>
       <c r="H89">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="I89">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J89">
-        <v>7.2328767123287676</v>
+        <v>0</v>
       </c>
       <c r="K89" s="2">
-        <v>109.37753424657535</v>
+        <v>108</v>
       </c>
       <c r="L89" s="2">
-        <v>0.57046666666666701</v>
+        <v>0.32444444444444476</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B90" s="1">
         <v>100</v>
       </c>
       <c r="C90" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D90" t="s">
         <v>19</v>
       </c>
       <c r="E90" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F90">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G90" t="s">
         <v>16</v>
       </c>
       <c r="H90">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="I90">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J90">
-        <v>10.849315068493151</v>
+        <v>0</v>
       </c>
       <c r="K90" s="2">
-        <v>113.06630136986303</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="L90" s="2">
-        <v>0.52991111111111133</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B91" s="1">
         <v>100</v>
       </c>
       <c r="C91" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D91" t="s">
         <v>19</v>
       </c>
       <c r="E91" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F91">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="G91" t="s">
         <v>16</v>
       </c>
       <c r="H91">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="I91">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J91">
-        <v>21.698630136986303</v>
+        <v>0</v>
       </c>
       <c r="K91" s="2">
-        <v>124.13260273972602</v>
+        <v>114.99999999999999</v>
       </c>
       <c r="L91" s="2">
-        <v>0.48935555555555532</v>
+        <v>0.36499999999999977</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B92" s="1">
         <v>100</v>
       </c>
       <c r="C92" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D92" t="s">
         <v>19</v>
       </c>
       <c r="E92" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F92">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="G92" t="s">
         <v>16</v>
       </c>
       <c r="H92">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="I92">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J92">
-        <v>32.547945205479458</v>
+        <v>0</v>
       </c>
       <c r="K92" s="2">
-        <v>135.19890410958905</v>
+        <v>118</v>
       </c>
       <c r="L92" s="2">
-        <v>0.47583703703703728</v>
+        <v>0.36499999999999982</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B93" s="1">
         <v>100</v>
       </c>
       <c r="C93" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D93" t="s">
         <v>19</v>
       </c>
       <c r="E93" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F93">
-        <v>360</v>
+        <v>60</v>
       </c>
       <c r="G93" t="s">
         <v>16</v>
       </c>
       <c r="H93">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="I93">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J93">
-        <v>43.397260273972606</v>
+        <v>0</v>
       </c>
       <c r="K93" s="2">
-        <v>146.26520547945205</v>
+        <v>106</v>
       </c>
       <c r="L93" s="2">
-        <v>0.46907777777777776</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B94" s="1">
         <v>100</v>
       </c>
       <c r="C94" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D94" t="s">
         <v>19</v>
       </c>
       <c r="E94" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F94">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G94" t="s">
         <v>16</v>
       </c>
       <c r="H94">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="I94">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J94">
-        <v>5.0958904109589049</v>
+        <v>0</v>
       </c>
       <c r="K94" s="2">
-        <v>107.19780821917809</v>
+        <v>108</v>
       </c>
       <c r="L94" s="2">
-        <v>0.43786666666666657</v>
+        <v>0.32444444444444476</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B95" s="1">
         <v>100</v>
       </c>
       <c r="C95" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D95" t="s">
         <v>19</v>
       </c>
       <c r="E95" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F95">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G95" t="s">
         <v>16</v>
       </c>
       <c r="H95">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="I95">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J95">
-        <v>7.6438356164383565</v>
+        <v>0</v>
       </c>
       <c r="K95" s="2">
-        <v>109.79671232876713</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="L95" s="2">
-        <v>0.39731111111111145</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B96" s="1">
         <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D96" t="s">
         <v>19</v>
       </c>
       <c r="E96" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F96">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="G96" t="s">
         <v>16</v>
       </c>
       <c r="H96">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="I96">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J96">
-        <v>15.287671232876713</v>
+        <v>0</v>
       </c>
       <c r="K96" s="2">
-        <v>117.59342465753424</v>
+        <v>114.99999999999999</v>
       </c>
       <c r="L96" s="2">
-        <v>0.35675555555555544</v>
+        <v>0.36499999999999977</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B97" s="1">
         <v>100</v>
       </c>
       <c r="C97" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D97" t="s">
         <v>19</v>
       </c>
       <c r="E97" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F97">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="G97" t="s">
         <v>16</v>
       </c>
       <c r="H97">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="I97">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J97">
-        <v>22.93150684931507</v>
+        <v>0</v>
       </c>
       <c r="K97" s="2">
-        <v>125.39013698630137</v>
+        <v>118</v>
       </c>
       <c r="L97" s="2">
-        <v>0.34323703703703701</v>
+        <v>0.36499999999999982</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B98" s="1">
         <v>100</v>
       </c>
       <c r="C98" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D98" t="s">
         <v>19</v>
       </c>
       <c r="E98" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F98">
-        <v>360</v>
+        <v>60</v>
       </c>
       <c r="G98" t="s">
         <v>16</v>
       </c>
       <c r="H98">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="I98">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J98">
-        <v>30.575342465753426</v>
+        <v>0</v>
       </c>
       <c r="K98" s="2">
-        <v>133.18684931506849</v>
+        <v>106</v>
       </c>
       <c r="L98" s="2">
-        <v>0.3364777777777776</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B99" s="1">
         <v>100</v>
       </c>
       <c r="C99" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D99" t="s">
         <v>19</v>
       </c>
       <c r="E99" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F99">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G99" t="s">
         <v>16</v>
       </c>
       <c r="H99">
-        <v>0.42499999999999999</v>
+        <v>0</v>
       </c>
       <c r="I99">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J99">
-        <v>6.9863013698630123</v>
+        <v>0</v>
       </c>
       <c r="K99" s="2">
-        <v>109.12602739726026</v>
+        <v>108</v>
       </c>
       <c r="L99" s="2">
-        <v>0.55516666666666514</v>
+        <v>0.32444444444444476</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B100" s="1">
         <v>100</v>
       </c>
       <c r="C100" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D100" t="s">
         <v>19</v>
       </c>
       <c r="E100" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F100">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G100" t="s">
         <v>16</v>
       </c>
       <c r="H100">
-        <v>0.42499999999999999</v>
+        <v>0</v>
       </c>
       <c r="I100">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J100">
-        <v>10.479452054794521</v>
+        <v>0</v>
       </c>
       <c r="K100" s="2">
-        <v>112.68904109589042</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="L100" s="2">
-        <v>0.51461111111111146</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B101" s="1">
         <v>100</v>
       </c>
       <c r="C101" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D101" t="s">
         <v>19</v>
       </c>
       <c r="E101" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F101">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="G101" t="s">
         <v>16</v>
       </c>
       <c r="H101">
-        <v>0.42499999999999999</v>
+        <v>0</v>
       </c>
       <c r="I101">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J101">
-        <v>20.958904109589042</v>
+        <v>0</v>
       </c>
       <c r="K101" s="2">
-        <v>123.37808219178083</v>
+        <v>114.99999999999999</v>
       </c>
       <c r="L101" s="2">
-        <v>0.47405555555555584</v>
+        <v>0.36499999999999977</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B102" s="1">
         <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D102" t="s">
         <v>19</v>
       </c>
       <c r="E102" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F102">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="G102" t="s">
         <v>16</v>
       </c>
       <c r="H102">
-        <v>0.42499999999999999</v>
+        <v>0</v>
       </c>
       <c r="I102">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J102">
-        <v>31.438356164383556</v>
+        <v>0</v>
       </c>
       <c r="K102" s="2">
-        <v>134.06712328767122</v>
+        <v>118</v>
       </c>
       <c r="L102" s="2">
-        <v>0.46053703703703697</v>
+        <v>0.36499999999999982</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B103" s="1">
         <v>100</v>
       </c>
       <c r="C103" t="s">
+        <v>25</v>
+      </c>
+      <c r="D103" t="s">
+        <v>19</v>
+      </c>
+      <c r="E103" t="s">
+        <v>14</v>
+      </c>
+      <c r="F103">
+        <v>60</v>
+      </c>
+      <c r="G103" t="s">
+        <v>16</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>6</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103" s="2">
+        <v>106</v>
+      </c>
+      <c r="L103" s="2">
+        <v>0.36500000000000032</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>33</v>
+      </c>
+      <c r="B104" s="1">
+        <v>100</v>
+      </c>
+      <c r="C104" t="s">
+        <v>25</v>
+      </c>
+      <c r="D104" t="s">
+        <v>19</v>
+      </c>
+      <c r="E104" t="s">
+        <v>14</v>
+      </c>
+      <c r="F104">
+        <v>90</v>
+      </c>
+      <c r="G104" t="s">
+        <v>16</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>8</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104" s="2">
+        <v>108</v>
+      </c>
+      <c r="L104" s="2">
+        <v>0.32444444444444476</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>33</v>
+      </c>
+      <c r="B105" s="1">
+        <v>100</v>
+      </c>
+      <c r="C105" t="s">
+        <v>25</v>
+      </c>
+      <c r="D105" t="s">
+        <v>19</v>
+      </c>
+      <c r="E105" t="s">
+        <v>14</v>
+      </c>
+      <c r="F105">
+        <v>120</v>
+      </c>
+      <c r="G105" t="s">
+        <v>16</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>12</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105" s="2">
+        <v>112.00000000000001</v>
+      </c>
+      <c r="L105" s="2">
+        <v>0.36500000000000032</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>33</v>
+      </c>
+      <c r="B106" s="1">
+        <v>100</v>
+      </c>
+      <c r="C106" t="s">
+        <v>25</v>
+      </c>
+      <c r="D106" t="s">
+        <v>19</v>
+      </c>
+      <c r="E106" t="s">
+        <v>14</v>
+      </c>
+      <c r="F106">
+        <v>150</v>
+      </c>
+      <c r="G106" t="s">
+        <v>16</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>15</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106" s="2">
+        <v>114.99999999999999</v>
+      </c>
+      <c r="L106" s="2">
+        <v>0.36499999999999977</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>33</v>
+      </c>
+      <c r="B107" s="1">
+        <v>100</v>
+      </c>
+      <c r="C107" t="s">
+        <v>25</v>
+      </c>
+      <c r="D107" t="s">
+        <v>19</v>
+      </c>
+      <c r="E107" t="s">
+        <v>14</v>
+      </c>
+      <c r="F107">
+        <v>180</v>
+      </c>
+      <c r="G107" t="s">
+        <v>16</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>18</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107" s="2">
+        <v>118</v>
+      </c>
+      <c r="L107" s="2">
+        <v>0.36499999999999982</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>33</v>
+      </c>
+      <c r="B108" s="1">
+        <v>100</v>
+      </c>
+      <c r="C108" t="s">
+        <v>26</v>
+      </c>
+      <c r="D108" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108" t="s">
+        <v>14</v>
+      </c>
+      <c r="F108">
+        <v>60</v>
+      </c>
+      <c r="G108" t="s">
+        <v>16</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <v>6</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108" s="2">
+        <v>106</v>
+      </c>
+      <c r="L108" s="2">
+        <v>0.36500000000000032</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>33</v>
+      </c>
+      <c r="B109" s="1">
+        <v>100</v>
+      </c>
+      <c r="C109" t="s">
+        <v>26</v>
+      </c>
+      <c r="D109" t="s">
+        <v>19</v>
+      </c>
+      <c r="E109" t="s">
+        <v>14</v>
+      </c>
+      <c r="F109">
+        <v>90</v>
+      </c>
+      <c r="G109" t="s">
+        <v>16</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <v>8</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109" s="2">
+        <v>108</v>
+      </c>
+      <c r="L109" s="2">
+        <v>0.32444444444444476</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>33</v>
+      </c>
+      <c r="B110" s="1">
+        <v>100</v>
+      </c>
+      <c r="C110" t="s">
+        <v>26</v>
+      </c>
+      <c r="D110" t="s">
+        <v>19</v>
+      </c>
+      <c r="E110" t="s">
+        <v>14</v>
+      </c>
+      <c r="F110">
+        <v>120</v>
+      </c>
+      <c r="G110" t="s">
+        <v>16</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>12</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110" s="2">
+        <v>112.00000000000001</v>
+      </c>
+      <c r="L110" s="2">
+        <v>0.36500000000000032</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>33</v>
+      </c>
+      <c r="B111" s="1">
+        <v>100</v>
+      </c>
+      <c r="C111" t="s">
+        <v>26</v>
+      </c>
+      <c r="D111" t="s">
+        <v>19</v>
+      </c>
+      <c r="E111" t="s">
+        <v>14</v>
+      </c>
+      <c r="F111">
+        <v>150</v>
+      </c>
+      <c r="G111" t="s">
+        <v>16</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>15</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111" s="2">
+        <v>114.99999999999999</v>
+      </c>
+      <c r="L111" s="2">
+        <v>0.36499999999999977</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>33</v>
+      </c>
+      <c r="B112" s="1">
+        <v>100</v>
+      </c>
+      <c r="C112" t="s">
+        <v>26</v>
+      </c>
+      <c r="D112" t="s">
+        <v>19</v>
+      </c>
+      <c r="E112" t="s">
+        <v>14</v>
+      </c>
+      <c r="F112">
+        <v>180</v>
+      </c>
+      <c r="G112" t="s">
+        <v>16</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>18</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112" s="2">
+        <v>118</v>
+      </c>
+      <c r="L112" s="2">
+        <v>0.36499999999999982</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>33</v>
+      </c>
+      <c r="B113" s="1">
+        <v>100</v>
+      </c>
+      <c r="C113" t="s">
+        <v>22</v>
+      </c>
+      <c r="D113" t="s">
+        <v>19</v>
+      </c>
+      <c r="E113" t="s">
+        <v>27</v>
+      </c>
+      <c r="F113">
+        <v>60</v>
+      </c>
+      <c r="G113" t="s">
+        <v>16</v>
+      </c>
+      <c r="H113">
+        <v>0.39137800925925947</v>
+      </c>
+      <c r="I113">
+        <v>2</v>
+      </c>
+      <c r="J113">
+        <v>6.4336111111111149</v>
+      </c>
+      <c r="K113" s="2">
+        <v>108.56228333333334</v>
+      </c>
+      <c r="L113" s="2">
+        <v>0.520872236111111</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>33</v>
+      </c>
+      <c r="B114" s="1">
+        <v>100</v>
+      </c>
+      <c r="C114" t="s">
+        <v>22</v>
+      </c>
+      <c r="D114" t="s">
+        <v>19</v>
+      </c>
+      <c r="E114" t="s">
+        <v>27</v>
+      </c>
+      <c r="F114">
+        <v>90</v>
+      </c>
+      <c r="G114" t="s">
+        <v>16</v>
+      </c>
+      <c r="H114">
+        <v>0.39760702340535009</v>
+      </c>
+      <c r="I114">
+        <v>2</v>
+      </c>
+      <c r="J114">
+        <v>9.804008796296305</v>
+      </c>
+      <c r="K114" s="2">
+        <v>112.00008897222223</v>
+      </c>
+      <c r="L114" s="2">
+        <v>0.48667027498456789</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>33</v>
+      </c>
+      <c r="B115" s="1">
+        <v>100</v>
+      </c>
+      <c r="C115" t="s">
+        <v>22</v>
+      </c>
+      <c r="D115" t="s">
+        <v>19</v>
+      </c>
+      <c r="E115" t="s">
+        <v>27</v>
+      </c>
+      <c r="F115">
+        <v>180</v>
+      </c>
+      <c r="G115" t="s">
+        <v>16</v>
+      </c>
+      <c r="H115">
+        <v>0.41709773718002596</v>
+      </c>
+      <c r="I115">
+        <v>2</v>
+      </c>
+      <c r="J115">
+        <v>20.569203477371147</v>
+      </c>
+      <c r="K115" s="2">
+        <v>122.98058754691857</v>
+      </c>
+      <c r="L115" s="2">
+        <v>0.46599524747918197</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>33</v>
+      </c>
+      <c r="B116" s="1">
+        <v>100</v>
+      </c>
+      <c r="C116" t="s">
+        <v>22</v>
+      </c>
+      <c r="D116" t="s">
+        <v>19</v>
+      </c>
+      <c r="E116" t="s">
+        <v>27</v>
+      </c>
+      <c r="F116">
+        <v>270</v>
+      </c>
+      <c r="G116" t="s">
+        <v>16</v>
+      </c>
+      <c r="H116">
+        <v>0.50397751875154939</v>
+      </c>
+      <c r="I116">
+        <v>2</v>
+      </c>
+      <c r="J116">
+        <v>37.280528784361188</v>
+      </c>
+      <c r="K116" s="2">
+        <v>140.0261393600484</v>
+      </c>
+      <c r="L116" s="2">
+        <v>0.54109410616361719</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>33</v>
+      </c>
+      <c r="B117" s="1">
+        <v>100</v>
+      </c>
+      <c r="C117" t="s">
+        <v>22</v>
+      </c>
+      <c r="D117" t="s">
+        <v>19</v>
+      </c>
+      <c r="E117" t="s">
+        <v>27</v>
+      </c>
+      <c r="F117">
+        <v>360</v>
+      </c>
+      <c r="G117" t="s">
+        <v>16</v>
+      </c>
+      <c r="H117">
+        <v>0.53303503052700441</v>
+      </c>
+      <c r="I117">
+        <v>2</v>
+      </c>
+      <c r="J117">
+        <v>52.573318079375774</v>
+      </c>
+      <c r="K117" s="2">
+        <v>155.62478444096328</v>
+      </c>
+      <c r="L117" s="2">
+        <v>0.56397350891532216</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>33</v>
+      </c>
+      <c r="B118" s="1">
+        <v>100</v>
+      </c>
+      <c r="C118" t="s">
+        <v>24</v>
+      </c>
+      <c r="D118" t="s">
+        <v>19</v>
+      </c>
+      <c r="E118" t="s">
+        <v>27</v>
+      </c>
+      <c r="F118">
+        <v>60</v>
+      </c>
+      <c r="G118" t="s">
+        <v>16</v>
+      </c>
+      <c r="H118">
+        <v>0.44</v>
+      </c>
+      <c r="I118">
+        <v>2</v>
+      </c>
+      <c r="J118">
+        <v>7.2328767123287676</v>
+      </c>
+      <c r="K118" s="2">
+        <v>109.37753424657535</v>
+      </c>
+      <c r="L118" s="2">
+        <v>0.57046666666666701</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>33</v>
+      </c>
+      <c r="B119" s="1">
+        <v>100</v>
+      </c>
+      <c r="C119" t="s">
+        <v>24</v>
+      </c>
+      <c r="D119" t="s">
+        <v>19</v>
+      </c>
+      <c r="E119" t="s">
+        <v>27</v>
+      </c>
+      <c r="F119">
+        <v>90</v>
+      </c>
+      <c r="G119" t="s">
+        <v>16</v>
+      </c>
+      <c r="H119">
+        <v>0.44</v>
+      </c>
+      <c r="I119">
+        <v>2</v>
+      </c>
+      <c r="J119">
+        <v>10.849315068493151</v>
+      </c>
+      <c r="K119" s="2">
+        <v>113.06630136986303</v>
+      </c>
+      <c r="L119" s="2">
+        <v>0.52991111111111133</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>33</v>
+      </c>
+      <c r="B120" s="1">
+        <v>100</v>
+      </c>
+      <c r="C120" t="s">
+        <v>24</v>
+      </c>
+      <c r="D120" t="s">
+        <v>19</v>
+      </c>
+      <c r="E120" t="s">
+        <v>27</v>
+      </c>
+      <c r="F120">
+        <v>180</v>
+      </c>
+      <c r="G120" t="s">
+        <v>16</v>
+      </c>
+      <c r="H120">
+        <v>0.44</v>
+      </c>
+      <c r="I120">
+        <v>2</v>
+      </c>
+      <c r="J120">
+        <v>21.698630136986303</v>
+      </c>
+      <c r="K120" s="2">
+        <v>124.13260273972602</v>
+      </c>
+      <c r="L120" s="2">
+        <v>0.48935555555555532</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>33</v>
+      </c>
+      <c r="B121" s="1">
+        <v>100</v>
+      </c>
+      <c r="C121" t="s">
+        <v>24</v>
+      </c>
+      <c r="D121" t="s">
+        <v>19</v>
+      </c>
+      <c r="E121" t="s">
+        <v>27</v>
+      </c>
+      <c r="F121">
+        <v>270</v>
+      </c>
+      <c r="G121" t="s">
+        <v>16</v>
+      </c>
+      <c r="H121">
+        <v>0.44</v>
+      </c>
+      <c r="I121">
+        <v>2</v>
+      </c>
+      <c r="J121">
+        <v>32.547945205479458</v>
+      </c>
+      <c r="K121" s="2">
+        <v>135.19890410958905</v>
+      </c>
+      <c r="L121" s="2">
+        <v>0.47583703703703728</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>33</v>
+      </c>
+      <c r="B122" s="1">
+        <v>100</v>
+      </c>
+      <c r="C122" t="s">
+        <v>24</v>
+      </c>
+      <c r="D122" t="s">
+        <v>19</v>
+      </c>
+      <c r="E122" t="s">
+        <v>27</v>
+      </c>
+      <c r="F122">
+        <v>360</v>
+      </c>
+      <c r="G122" t="s">
+        <v>16</v>
+      </c>
+      <c r="H122">
+        <v>0.44</v>
+      </c>
+      <c r="I122">
+        <v>2</v>
+      </c>
+      <c r="J122">
+        <v>43.397260273972606</v>
+      </c>
+      <c r="K122" s="2">
+        <v>146.26520547945205</v>
+      </c>
+      <c r="L122" s="2">
+        <v>0.46907777777777776</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>33</v>
+      </c>
+      <c r="B123" s="1">
+        <v>100</v>
+      </c>
+      <c r="C123" t="s">
         <v>28</v>
       </c>
-      <c r="D103" t="s">
-        <v>19</v>
-      </c>
-      <c r="E103" t="s">
-        <v>26</v>
-      </c>
-      <c r="F103">
+      <c r="D123" t="s">
+        <v>19</v>
+      </c>
+      <c r="E123" t="s">
+        <v>27</v>
+      </c>
+      <c r="F123">
+        <v>60</v>
+      </c>
+      <c r="G123" t="s">
+        <v>16</v>
+      </c>
+      <c r="H123">
+        <v>0.31</v>
+      </c>
+      <c r="I123">
+        <v>2</v>
+      </c>
+      <c r="J123">
+        <v>5.0958904109589049</v>
+      </c>
+      <c r="K123" s="2">
+        <v>107.19780821917809</v>
+      </c>
+      <c r="L123" s="2">
+        <v>0.43786666666666657</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>33</v>
+      </c>
+      <c r="B124" s="1">
+        <v>100</v>
+      </c>
+      <c r="C124" t="s">
+        <v>28</v>
+      </c>
+      <c r="D124" t="s">
+        <v>19</v>
+      </c>
+      <c r="E124" t="s">
+        <v>27</v>
+      </c>
+      <c r="F124">
+        <v>90</v>
+      </c>
+      <c r="G124" t="s">
+        <v>16</v>
+      </c>
+      <c r="H124">
+        <v>0.31</v>
+      </c>
+      <c r="I124">
+        <v>2</v>
+      </c>
+      <c r="J124">
+        <v>7.6438356164383565</v>
+      </c>
+      <c r="K124" s="2">
+        <v>109.79671232876713</v>
+      </c>
+      <c r="L124" s="2">
+        <v>0.39731111111111145</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>33</v>
+      </c>
+      <c r="B125" s="1">
+        <v>100</v>
+      </c>
+      <c r="C125" t="s">
+        <v>28</v>
+      </c>
+      <c r="D125" t="s">
+        <v>19</v>
+      </c>
+      <c r="E125" t="s">
+        <v>27</v>
+      </c>
+      <c r="F125">
+        <v>180</v>
+      </c>
+      <c r="G125" t="s">
+        <v>16</v>
+      </c>
+      <c r="H125">
+        <v>0.31</v>
+      </c>
+      <c r="I125">
+        <v>2</v>
+      </c>
+      <c r="J125">
+        <v>15.287671232876713</v>
+      </c>
+      <c r="K125" s="2">
+        <v>117.59342465753424</v>
+      </c>
+      <c r="L125" s="2">
+        <v>0.35675555555555544</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>33</v>
+      </c>
+      <c r="B126" s="1">
+        <v>100</v>
+      </c>
+      <c r="C126" t="s">
+        <v>28</v>
+      </c>
+      <c r="D126" t="s">
+        <v>19</v>
+      </c>
+      <c r="E126" t="s">
+        <v>27</v>
+      </c>
+      <c r="F126">
+        <v>270</v>
+      </c>
+      <c r="G126" t="s">
+        <v>16</v>
+      </c>
+      <c r="H126">
+        <v>0.31</v>
+      </c>
+      <c r="I126">
+        <v>2</v>
+      </c>
+      <c r="J126">
+        <v>22.93150684931507</v>
+      </c>
+      <c r="K126" s="2">
+        <v>125.39013698630137</v>
+      </c>
+      <c r="L126" s="2">
+        <v>0.34323703703703701</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>33</v>
+      </c>
+      <c r="B127" s="1">
+        <v>100</v>
+      </c>
+      <c r="C127" t="s">
+        <v>28</v>
+      </c>
+      <c r="D127" t="s">
+        <v>19</v>
+      </c>
+      <c r="E127" t="s">
+        <v>27</v>
+      </c>
+      <c r="F127">
         <v>360</v>
       </c>
-      <c r="G103" t="s">
-        <v>16</v>
-      </c>
-      <c r="H103">
+      <c r="G127" t="s">
+        <v>16</v>
+      </c>
+      <c r="H127">
+        <v>0.31</v>
+      </c>
+      <c r="I127">
+        <v>2</v>
+      </c>
+      <c r="J127">
+        <v>30.575342465753426</v>
+      </c>
+      <c r="K127" s="2">
+        <v>133.18684931506849</v>
+      </c>
+      <c r="L127" s="2">
+        <v>0.3364777777777776</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>33</v>
+      </c>
+      <c r="B128" s="1">
+        <v>100</v>
+      </c>
+      <c r="C128" t="s">
+        <v>29</v>
+      </c>
+      <c r="D128" t="s">
+        <v>19</v>
+      </c>
+      <c r="E128" t="s">
+        <v>27</v>
+      </c>
+      <c r="F128">
+        <v>60</v>
+      </c>
+      <c r="G128" t="s">
+        <v>16</v>
+      </c>
+      <c r="H128">
         <v>0.42499999999999999</v>
       </c>
-      <c r="I103">
+      <c r="I128">
         <v>2</v>
       </c>
-      <c r="J103">
+      <c r="J128">
+        <v>6.9863013698630123</v>
+      </c>
+      <c r="K128" s="2">
+        <v>109.12602739726026</v>
+      </c>
+      <c r="L128" s="2">
+        <v>0.55516666666666514</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>33</v>
+      </c>
+      <c r="B129" s="1">
+        <v>100</v>
+      </c>
+      <c r="C129" t="s">
+        <v>29</v>
+      </c>
+      <c r="D129" t="s">
+        <v>19</v>
+      </c>
+      <c r="E129" t="s">
+        <v>27</v>
+      </c>
+      <c r="F129">
+        <v>90</v>
+      </c>
+      <c r="G129" t="s">
+        <v>16</v>
+      </c>
+      <c r="H129">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="I129">
+        <v>2</v>
+      </c>
+      <c r="J129">
+        <v>10.479452054794521</v>
+      </c>
+      <c r="K129" s="2">
+        <v>112.68904109589042</v>
+      </c>
+      <c r="L129" s="2">
+        <v>0.51461111111111146</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>33</v>
+      </c>
+      <c r="B130" s="1">
+        <v>100</v>
+      </c>
+      <c r="C130" t="s">
+        <v>29</v>
+      </c>
+      <c r="D130" t="s">
+        <v>19</v>
+      </c>
+      <c r="E130" t="s">
+        <v>27</v>
+      </c>
+      <c r="F130">
+        <v>180</v>
+      </c>
+      <c r="G130" t="s">
+        <v>16</v>
+      </c>
+      <c r="H130">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="I130">
+        <v>2</v>
+      </c>
+      <c r="J130">
+        <v>20.958904109589042</v>
+      </c>
+      <c r="K130" s="2">
+        <v>123.37808219178083</v>
+      </c>
+      <c r="L130" s="2">
+        <v>0.47405555555555584</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>33</v>
+      </c>
+      <c r="B131" s="1">
+        <v>100</v>
+      </c>
+      <c r="C131" t="s">
+        <v>29</v>
+      </c>
+      <c r="D131" t="s">
+        <v>19</v>
+      </c>
+      <c r="E131" t="s">
+        <v>27</v>
+      </c>
+      <c r="F131">
+        <v>270</v>
+      </c>
+      <c r="G131" t="s">
+        <v>16</v>
+      </c>
+      <c r="H131">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="I131">
+        <v>2</v>
+      </c>
+      <c r="J131">
+        <v>31.438356164383556</v>
+      </c>
+      <c r="K131" s="2">
+        <v>134.06712328767122</v>
+      </c>
+      <c r="L131" s="2">
+        <v>0.46053703703703697</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>33</v>
+      </c>
+      <c r="B132" s="1">
+        <v>100</v>
+      </c>
+      <c r="C132" t="s">
+        <v>29</v>
+      </c>
+      <c r="D132" t="s">
+        <v>19</v>
+      </c>
+      <c r="E132" t="s">
+        <v>27</v>
+      </c>
+      <c r="F132">
+        <v>360</v>
+      </c>
+      <c r="G132" t="s">
+        <v>16</v>
+      </c>
+      <c r="H132">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="I132">
+        <v>2</v>
+      </c>
+      <c r="J132">
         <v>41.917808219178085</v>
       </c>
-      <c r="K103" s="2">
+      <c r="K132" s="2">
         <v>144.75616438356164</v>
       </c>
-      <c r="L103" s="2">
+      <c r="L132" s="2">
         <v>0.45377777777777778</v>
       </c>
     </row>

--- a/public/datos.xlsx
+++ b/public/datos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NicolasAcebo\OneDrive - LARTIRIGOYEN Y CIA. S.A\Escritorio\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Financiera\Gestion Financiera\Condiciones Comerciales - Convenios Tarjetas\Simulador online\simulador ok\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D3184F-D985-46DE-AB02-FA1DD604AB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB08C33-99FE-4009-9DBB-A5E8CFB2ED99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5F5C8F4A-A9C3-4394-B81C-80D194F2AEAA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="39">
   <si>
     <t>Precio de contado</t>
   </si>
@@ -538,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7F38534-621C-456A-88D0-E73BF73C904A}">
-  <dimension ref="A1:L132"/>
+  <dimension ref="A1:L130"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
@@ -605,19 +605,19 @@
         <v>13</v>
       </c>
       <c r="H2">
-        <v>5.5E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="I2">
         <v>1.7999999999999998</v>
       </c>
       <c r="J2">
-        <v>2.7123287671232879</v>
+        <v>3.2054794520547945</v>
       </c>
       <c r="K2" s="2">
-        <v>104.5611506849315</v>
+        <v>105.06317808219178</v>
       </c>
       <c r="L2" s="2">
-        <v>9.2489999999999919E-2</v>
+        <v>0.10267000000000015</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -646,16 +646,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>4.3999999999999995</v>
+        <v>5</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" s="2">
-        <v>104.4</v>
+        <v>105</v>
       </c>
       <c r="L3" s="2">
-        <v>8.92222222222223E-2</v>
+        <v>0.10138888888888899</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -681,19 +681,19 @@
         <v>13</v>
       </c>
       <c r="H4">
-        <v>7.0000000000000007E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="I4">
         <v>1.7999999999999998</v>
       </c>
       <c r="J4">
-        <v>5.1780821917808222</v>
+        <v>5.5479452054794516</v>
       </c>
       <c r="K4" s="2">
-        <v>107.07128767123287</v>
+        <v>107.44780821917809</v>
       </c>
       <c r="L4" s="2">
-        <v>9.5593333333333141E-2</v>
+        <v>0.10068333333333326</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -722,16 +722,16 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>7.0000000000000009</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" s="2">
-        <v>107</v>
+        <v>107.5</v>
       </c>
       <c r="L5" s="2">
-        <v>9.4629629629629716E-2</v>
+        <v>0.10138888888888883</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -812,7 +812,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" s="1">
         <v>100</v>
@@ -827,25 +827,25 @@
         <v>12</v>
       </c>
       <c r="F8">
-        <v>420</v>
+        <v>180</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
       </c>
       <c r="H8">
-        <v>9.5000000000000001E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="I8">
         <v>1.7999999999999998</v>
       </c>
       <c r="J8">
-        <v>10.931506849315067</v>
+        <v>3.2054794520547945</v>
       </c>
       <c r="K8" s="2">
-        <v>112.92827397260274</v>
+        <v>105.06317808219178</v>
       </c>
       <c r="L8" s="2">
-        <v>0.11235285714285718</v>
+        <v>0.10267000000000015</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -862,7 +862,7 @@
         <v>11</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F9">
         <v>180</v>
@@ -871,19 +871,19 @@
         <v>13</v>
       </c>
       <c r="H9">
-        <v>5.5E-2</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>1.7999999999999998</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>2.7123287671232879</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2">
-        <v>104.5611506849315</v>
+        <v>105</v>
       </c>
       <c r="L9" s="2">
-        <v>9.2489999999999919E-2</v>
+        <v>0.10138888888888899</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -900,28 +900,28 @@
         <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="I10">
-        <v>4.3999999999999995</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>5.5479452054794516</v>
       </c>
       <c r="K10" s="2">
-        <v>104.4</v>
+        <v>107.44780821917809</v>
       </c>
       <c r="L10" s="2">
-        <v>8.92222222222223E-2</v>
+        <v>0.10068333333333326</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -938,7 +938,7 @@
         <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F11">
         <v>270</v>
@@ -947,19 +947,19 @@
         <v>13</v>
       </c>
       <c r="H11">
-        <v>7.0000000000000007E-2</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>1.7999999999999998</v>
+        <v>7.5</v>
       </c>
       <c r="J11">
-        <v>5.1780821917808222</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2">
-        <v>107.07128767123287</v>
+        <v>107.5</v>
       </c>
       <c r="L11" s="2">
-        <v>9.5593333333333141E-2</v>
+        <v>0.10138888888888883</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -976,28 +976,28 @@
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F12">
-        <v>270</v>
+        <v>360</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="I12">
-        <v>7.0000000000000009</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>8.383561643835618</v>
       </c>
       <c r="K12" s="2">
-        <v>107</v>
+        <v>110.33446575342467</v>
       </c>
       <c r="L12" s="2">
-        <v>9.4629629629629716E-2</v>
+        <v>0.10478000000000014</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1014,7 +1014,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F13">
         <v>360</v>
@@ -1023,68 +1023,68 @@
         <v>13</v>
       </c>
       <c r="H13">
-        <v>8.5000000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>1.7999999999999998</v>
+        <v>10.299999999999999</v>
       </c>
       <c r="J13">
-        <v>8.383561643835618</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2">
-        <v>110.33446575342467</v>
+        <v>110.3</v>
       </c>
       <c r="L13" s="2">
-        <v>0.10478000000000014</v>
+        <v>0.10443055555555554</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1">
         <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F14">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="I14">
-        <v>10.299999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1.6027397260273972</v>
       </c>
       <c r="K14" s="2">
-        <v>110.3</v>
+        <v>104.75242465753425</v>
       </c>
       <c r="L14" s="2">
-        <v>0.10443055555555554</v>
+        <v>0.19273722222222231</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B15" s="1">
         <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -1093,25 +1093,25 @@
         <v>12</v>
       </c>
       <c r="F15">
-        <v>420</v>
+        <v>180</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
       </c>
       <c r="H15">
-        <v>9.5000000000000001E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="I15">
-        <v>1.7999999999999998</v>
+        <v>3.1</v>
       </c>
       <c r="J15">
-        <v>10.931506849315067</v>
+        <v>3.2054794520547945</v>
       </c>
       <c r="K15" s="2">
-        <v>112.92827397260274</v>
+        <v>106.4048493150685</v>
       </c>
       <c r="L15" s="2">
-        <v>0.11235285714285718</v>
+        <v>0.12987611111111139</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1131,25 +1131,25 @@
         <v>12</v>
       </c>
       <c r="F16">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
       </c>
       <c r="H16">
-        <v>6.5000000000000002E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="I16">
         <v>3.1</v>
       </c>
       <c r="J16">
-        <v>1.6027397260273972</v>
+        <v>5.5479452054794516</v>
       </c>
       <c r="K16" s="2">
-        <v>104.75242465753425</v>
+        <v>108.81993150684931</v>
       </c>
       <c r="L16" s="2">
-        <v>0.19273722222222231</v>
+        <v>0.1192324074074075</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1169,25 +1169,25 @@
         <v>12</v>
       </c>
       <c r="F17">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
       </c>
       <c r="H17">
-        <v>6.5000000000000002E-2</v>
+        <v>0.09</v>
       </c>
       <c r="I17">
         <v>3.1</v>
       </c>
       <c r="J17">
-        <v>3.2054794520547945</v>
+        <v>8.8767123287671232</v>
       </c>
       <c r="K17" s="2">
-        <v>106.4048493150685</v>
+        <v>112.25189041095889</v>
       </c>
       <c r="L17" s="2">
-        <v>0.12987611111111139</v>
+        <v>0.1242205555555554</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1198,34 +1198,34 @@
         <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F18">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
       </c>
       <c r="H18">
-        <v>7.4999999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>5.5479452054794516</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2">
-        <v>108.81993150684931</v>
+        <v>105</v>
       </c>
       <c r="L18" s="2">
-        <v>0.1192324074074075</v>
+        <v>0.10138888888888899</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1236,34 +1236,34 @@
         <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F19">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
       </c>
       <c r="H19">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>3.1</v>
+        <v>7.6</v>
       </c>
       <c r="J19">
-        <v>8.8767123287671232</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2">
-        <v>112.25189041095889</v>
+        <v>107.60000000000001</v>
       </c>
       <c r="L19" s="2">
-        <v>0.1242205555555554</v>
+        <v>0.10274074074074083</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1283,7 +1283,7 @@
         <v>14</v>
       </c>
       <c r="F20">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -1292,16 +1292,16 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>5.4</v>
+        <v>11.600000000000001</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20" s="2">
-        <v>105.4</v>
+        <v>111.60000000000001</v>
       </c>
       <c r="L20" s="2">
-        <v>0.10950000000000008</v>
+        <v>0.11761111111111121</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1318,28 +1318,28 @@
         <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F21">
-        <v>270</v>
+        <v>360</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="I21">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>10.356164383561643</v>
       </c>
       <c r="K21" s="2">
-        <v>109.00000000000001</v>
+        <v>111.45972602739725</v>
       </c>
       <c r="L21" s="2">
-        <v>0.12166666666666678</v>
+        <v>0.11618888888888872</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1350,34 +1350,34 @@
         <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F22">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="I22">
-        <v>11.600000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>0.73972602739726023</v>
       </c>
       <c r="K22" s="2">
-        <v>111.60000000000001</v>
+        <v>102.8552602739726</v>
       </c>
       <c r="L22" s="2">
-        <v>0.11761111111111121</v>
+        <v>5.7898333333333364E-2</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -1388,7 +1388,7 @@
         <v>100</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -1397,25 +1397,25 @@
         <v>12</v>
       </c>
       <c r="F23">
-        <v>360</v>
+        <v>210</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
       <c r="H23">
-        <v>0.105</v>
+        <v>0.02</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J23">
-        <v>10.356164383561643</v>
+        <v>1.1506849315068493</v>
       </c>
       <c r="K23" s="2">
-        <v>111.45972602739725</v>
+        <v>103.27484931506849</v>
       </c>
       <c r="L23" s="2">
-        <v>0.11618888888888872</v>
+        <v>5.692000000000004E-2</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -1435,36 +1435,36 @@
         <v>12</v>
       </c>
       <c r="F24">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24">
-        <v>1.4999999999999999E-2</v>
+        <v>0.03</v>
       </c>
       <c r="I24">
         <v>2.1</v>
       </c>
       <c r="J24">
-        <v>0.73972602739726023</v>
+        <v>2.2191780821917808</v>
       </c>
       <c r="K24" s="2">
-        <v>102.8552602739726</v>
+        <v>104.36578082191781</v>
       </c>
       <c r="L24" s="2">
-        <v>5.7898333333333364E-2</v>
+        <v>5.9018888888888899E-2</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B25" s="1">
         <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
@@ -1473,36 +1473,36 @@
         <v>12</v>
       </c>
       <c r="F25">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="G25" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H25">
-        <v>0.02</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I25">
-        <v>2.1</v>
+        <v>6.5</v>
       </c>
       <c r="J25">
-        <v>1.1506849315068493</v>
+        <v>13.808219178082194</v>
       </c>
       <c r="K25" s="2">
-        <v>103.27484931506849</v>
+        <v>121.20575342465753</v>
       </c>
       <c r="L25" s="2">
-        <v>5.692000000000004E-2</v>
+        <v>0.43000555555555559</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B26" s="1">
         <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
@@ -1514,22 +1514,22 @@
         <v>270</v>
       </c>
       <c r="G26" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H26">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="I26">
-        <v>2.1</v>
+        <v>7.5</v>
       </c>
       <c r="J26">
-        <v>2.2191780821917808</v>
+        <v>22.191780821917806</v>
       </c>
       <c r="K26" s="2">
-        <v>104.36578082191781</v>
+        <v>131.35616438356166</v>
       </c>
       <c r="L26" s="2">
-        <v>5.9018888888888899E-2</v>
+        <v>0.42388888888888909</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -1549,30 +1549,30 @@
         <v>12</v>
       </c>
       <c r="F27">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="G27" t="s">
         <v>16</v>
       </c>
       <c r="H27">
-        <v>0.28000000000000003</v>
+        <v>0.3</v>
       </c>
       <c r="I27">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>13.808219178082194</v>
+        <v>29.589041095890412</v>
       </c>
       <c r="K27" s="2">
-        <v>121.20575342465753</v>
+        <v>142.54794520547949</v>
       </c>
       <c r="L27" s="2">
-        <v>0.43000555555555559</v>
+        <v>0.43138888888888927</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" s="1">
         <v>100</v>
@@ -1587,30 +1587,30 @@
         <v>12</v>
       </c>
       <c r="F28">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="G28" t="s">
         <v>16</v>
       </c>
       <c r="H28">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="I28">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="J28">
-        <v>22.191780821917806</v>
+        <v>17.260273972602739</v>
       </c>
       <c r="K28" s="2">
-        <v>131.35616438356166</v>
+        <v>124.88219178082193</v>
       </c>
       <c r="L28" s="2">
-        <v>0.42388888888888909</v>
+        <v>0.50455555555555553</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" s="1">
         <v>100</v>
@@ -1625,25 +1625,25 @@
         <v>12</v>
       </c>
       <c r="F29">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="G29" t="s">
         <v>16</v>
       </c>
       <c r="H29">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="I29">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="J29">
-        <v>29.589041095890412</v>
+        <v>27.36986301369863</v>
       </c>
       <c r="K29" s="2">
-        <v>142.54794520547949</v>
+        <v>136.92260273972605</v>
       </c>
       <c r="L29" s="2">
-        <v>0.43138888888888927</v>
+        <v>0.49913888888888924</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -1663,36 +1663,36 @@
         <v>12</v>
       </c>
       <c r="F30">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="G30" t="s">
         <v>16</v>
       </c>
       <c r="H30">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="I30">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>17.260273972602739</v>
+        <v>36.493150684931507</v>
       </c>
       <c r="K30" s="2">
-        <v>124.88219178082193</v>
+        <v>150.14246575342469</v>
       </c>
       <c r="L30" s="2">
-        <v>0.50455555555555553</v>
+        <v>0.50838888888888922</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" s="1">
         <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
@@ -1701,36 +1701,36 @@
         <v>12</v>
       </c>
       <c r="F31">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="G31" t="s">
         <v>16</v>
       </c>
       <c r="H31">
-        <v>0.37</v>
+        <v>0.255</v>
       </c>
       <c r="I31">
-        <v>7.5</v>
+        <v>13.4</v>
       </c>
       <c r="J31">
-        <v>27.36986301369863</v>
+        <v>12.575342465753426</v>
       </c>
       <c r="K31" s="2">
-        <v>136.92260273972605</v>
+        <v>127.66043835616438</v>
       </c>
       <c r="L31" s="2">
-        <v>0.49913888888888924</v>
+        <v>0.56089222222222224</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="1">
         <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
@@ -1739,25 +1739,25 @@
         <v>12</v>
       </c>
       <c r="F32">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="G32" t="s">
         <v>16</v>
       </c>
       <c r="H32">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="I32">
-        <v>10</v>
+        <v>13.4</v>
       </c>
       <c r="J32">
-        <v>36.493150684931507</v>
+        <v>26.630136986301366</v>
       </c>
       <c r="K32" s="2">
-        <v>150.14246575342469</v>
+        <v>143.59857534246575</v>
       </c>
       <c r="L32" s="2">
-        <v>0.50838888888888922</v>
+        <v>0.58938814814814799</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -1777,30 +1777,30 @@
         <v>12</v>
       </c>
       <c r="F33">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="G33" t="s">
         <v>16</v>
       </c>
       <c r="H33">
-        <v>0.255</v>
+        <v>0.45</v>
       </c>
       <c r="I33">
-        <v>12.311111111111112</v>
+        <v>13.4</v>
       </c>
       <c r="J33">
-        <v>12.575342465753426</v>
+        <v>44.38356164383562</v>
       </c>
       <c r="K33" s="2">
-        <v>126.43461796042618</v>
+        <v>163.73095890410957</v>
       </c>
       <c r="L33" s="2">
-        <v>0.53603530864197546</v>
+        <v>0.64616111111111108</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" s="1">
         <v>100</v>
@@ -1811,34 +1811,34 @@
       <c r="D34" t="s">
         <v>11</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" t="s">
         <v>12</v>
       </c>
       <c r="F34">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="G34" t="s">
         <v>16</v>
       </c>
       <c r="H34">
-        <v>0.36</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I34">
-        <v>12.311111111111112</v>
+        <v>13.4</v>
       </c>
       <c r="J34">
-        <v>26.630136986301366</v>
+        <v>13.808219178082194</v>
       </c>
       <c r="K34" s="2">
-        <v>142.21971385083714</v>
+        <v>129.05852054794519</v>
       </c>
       <c r="L34" s="2">
-        <v>0.57074798353909462</v>
+        <v>0.58924222222222211</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B35" s="1">
         <v>100</v>
@@ -1849,29 +1849,29 @@
       <c r="D35" t="s">
         <v>11</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" t="s">
         <v>12</v>
       </c>
       <c r="F35">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="G35" t="s">
         <v>16</v>
       </c>
       <c r="H35">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="I35">
-        <v>12.311111111111112</v>
+        <v>13.4</v>
       </c>
       <c r="J35">
-        <v>44.38356164383562</v>
+        <v>28.849315068493155</v>
       </c>
       <c r="K35" s="2">
-        <v>162.15878234398784</v>
+        <v>146.11512328767122</v>
       </c>
       <c r="L35" s="2">
-        <v>0.63022098765432122</v>
+        <v>0.62340814814814804</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -1891,36 +1891,36 @@
         <v>12</v>
       </c>
       <c r="F36">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="G36" t="s">
         <v>16</v>
       </c>
       <c r="H36">
-        <v>0.28000000000000003</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="I36">
-        <v>12.311111111111112</v>
+        <v>13.4</v>
       </c>
       <c r="J36">
-        <v>13.808219178082194</v>
+        <v>46.849315068493155</v>
       </c>
       <c r="K36" s="2">
-        <v>127.81927549467277</v>
+        <v>166.5271232876712</v>
       </c>
       <c r="L36" s="2">
-        <v>0.56411308641975311</v>
+        <v>0.67451111111111095</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B37" s="1">
         <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
@@ -1929,36 +1929,36 @@
         <v>12</v>
       </c>
       <c r="F37">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="G37" t="s">
         <v>16</v>
       </c>
       <c r="H37">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="I37">
-        <v>12.311111111111112</v>
+        <v>3.1</v>
       </c>
       <c r="J37">
-        <v>28.849315068493155</v>
+        <v>16.767123287671236</v>
       </c>
       <c r="K37" s="2">
-        <v>144.71209741248097</v>
+        <v>120.38690410958905</v>
       </c>
       <c r="L37" s="2">
-        <v>0.60444131687242786</v>
+        <v>0.41340111111111133</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B38" s="1">
         <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D38" t="s">
         <v>11</v>
@@ -1967,25 +1967,25 @@
         <v>12</v>
       </c>
       <c r="F38">
-        <v>360</v>
+        <v>210</v>
       </c>
       <c r="G38" t="s">
         <v>16</v>
       </c>
       <c r="H38">
-        <v>0.47499999999999998</v>
+        <v>0.36</v>
       </c>
       <c r="I38">
-        <v>12.311111111111112</v>
+        <v>3.1</v>
       </c>
       <c r="J38">
-        <v>46.849315068493155</v>
+        <v>20.712328767123285</v>
       </c>
       <c r="K38" s="2">
-        <v>164.92809741248098</v>
+        <v>124.45441095890409</v>
       </c>
       <c r="L38" s="2">
-        <v>0.65829876543209875</v>
+        <v>0.42504095238095191</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -2005,25 +2005,25 @@
         <v>12</v>
       </c>
       <c r="F39">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="G39" t="s">
         <v>16</v>
       </c>
       <c r="H39">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="I39">
         <v>3.1</v>
       </c>
       <c r="J39">
-        <v>16.767123287671236</v>
+        <v>27.36986301369863</v>
       </c>
       <c r="K39" s="2">
-        <v>120.38690410958905</v>
+        <v>131.31832876712329</v>
       </c>
       <c r="L39" s="2">
-        <v>0.41340111111111133</v>
+        <v>0.42337740740740737</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -2043,36 +2043,36 @@
         <v>12</v>
       </c>
       <c r="F40">
-        <v>210</v>
+        <v>360</v>
       </c>
       <c r="G40" t="s">
         <v>16</v>
       </c>
       <c r="H40">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="I40">
         <v>3.1</v>
       </c>
       <c r="J40">
-        <v>20.712328767123285</v>
+        <v>39.452054794520549</v>
       </c>
       <c r="K40" s="2">
-        <v>124.45441095890409</v>
+        <v>143.77506849315068</v>
       </c>
       <c r="L40" s="2">
-        <v>0.42504095238095191</v>
+        <v>0.44383055555555562</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B41" s="1">
         <v>100</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
@@ -2081,36 +2081,36 @@
         <v>12</v>
       </c>
       <c r="F41">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="G41" t="s">
         <v>16</v>
       </c>
       <c r="H41">
-        <v>0.37</v>
+        <v>0.38540000000000002</v>
       </c>
       <c r="I41">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="J41">
-        <v>27.36986301369863</v>
+        <v>19.006027397260276</v>
       </c>
       <c r="K41" s="2">
-        <v>131.31832876712329</v>
+        <v>125.31334684931507</v>
       </c>
       <c r="L41" s="2">
-        <v>0.42337740740740737</v>
+        <v>0.51329842222222244</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B42" s="1">
         <v>100</v>
       </c>
       <c r="C42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
@@ -2119,30 +2119,30 @@
         <v>12</v>
       </c>
       <c r="F42">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="G42" t="s">
         <v>16</v>
       </c>
       <c r="H42">
-        <v>0.4</v>
+        <v>0.47970000000000002</v>
       </c>
       <c r="I42">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="J42">
-        <v>39.452054794520549</v>
+        <v>31.541917808219178</v>
       </c>
       <c r="K42" s="2">
-        <v>143.77506849315068</v>
+        <v>138.5136394520548</v>
       </c>
       <c r="L42" s="2">
-        <v>0.44383055555555562</v>
+        <v>0.58572826666666666</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B43" s="1">
         <v>100</v>
@@ -2163,24 +2163,24 @@
         <v>16</v>
       </c>
       <c r="H43">
-        <v>0.38540000000000002</v>
+        <v>0.43330000000000002</v>
       </c>
       <c r="I43">
         <v>5.3</v>
       </c>
       <c r="J43">
-        <v>19.006027397260276</v>
+        <v>21.368219178082192</v>
       </c>
       <c r="K43" s="2">
-        <v>125.31334684931507</v>
+        <v>127.80073479452054</v>
       </c>
       <c r="L43" s="2">
-        <v>0.51329842222222244</v>
+        <v>0.56373712222222205</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B44" s="1">
         <v>100</v>
@@ -2201,30 +2201,30 @@
         <v>16</v>
       </c>
       <c r="H44">
-        <v>0.47970000000000002</v>
+        <v>0.50339999999999996</v>
       </c>
       <c r="I44">
         <v>5.3</v>
       </c>
       <c r="J44">
-        <v>31.541917808219178</v>
+        <v>33.100273972602743</v>
       </c>
       <c r="K44" s="2">
-        <v>138.5136394520548</v>
+        <v>140.15458849315067</v>
       </c>
       <c r="L44" s="2">
-        <v>0.58572826666666666</v>
+        <v>0.61068436666666659</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B45" s="1">
         <v>100</v>
       </c>
       <c r="C45" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D45" t="s">
         <v>11</v>
@@ -2239,30 +2239,30 @@
         <v>16</v>
       </c>
       <c r="H45">
-        <v>0.43330000000000002</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="I45">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="J45">
-        <v>21.368219178082192</v>
+        <v>19.972602739726028</v>
       </c>
       <c r="K45" s="2">
-        <v>127.80073479452054</v>
+        <v>122.37205479452055</v>
       </c>
       <c r="L45" s="2">
-        <v>0.56373712222222205</v>
+        <v>0.45365555555555576</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B46" s="1">
         <v>100</v>
       </c>
       <c r="C46" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D46" t="s">
         <v>11</v>
@@ -2271,25 +2271,25 @@
         <v>12</v>
       </c>
       <c r="F46">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="G46" t="s">
         <v>16</v>
       </c>
       <c r="H46">
-        <v>0.50339999999999996</v>
+        <v>0.41</v>
       </c>
       <c r="I46">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="J46">
-        <v>33.100273972602743</v>
+        <v>23.589041095890412</v>
       </c>
       <c r="K46" s="2">
-        <v>140.15458849315067</v>
+        <v>126.06082191780823</v>
       </c>
       <c r="L46" s="2">
-        <v>0.61068436666666659</v>
+        <v>0.4529619047619049</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -2309,36 +2309,36 @@
         <v>12</v>
       </c>
       <c r="F47">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="G47" t="s">
         <v>16</v>
       </c>
       <c r="H47">
-        <v>0.40500000000000003</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="I47">
         <v>2</v>
       </c>
       <c r="J47">
-        <v>19.972602739726028</v>
+        <v>30.698630136986299</v>
       </c>
       <c r="K47" s="2">
-        <v>122.37205479452055</v>
+        <v>133.31260273972603</v>
       </c>
       <c r="L47" s="2">
-        <v>0.45365555555555576</v>
+        <v>0.45033703703703704</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B48" s="1">
         <v>100</v>
       </c>
       <c r="C48" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D48" t="s">
         <v>11</v>
@@ -2347,36 +2347,36 @@
         <v>12</v>
       </c>
       <c r="F48">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="G48" t="s">
         <v>16</v>
       </c>
       <c r="H48">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="I48">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J48">
-        <v>23.589041095890412</v>
+        <v>21.698630136986303</v>
       </c>
       <c r="K48" s="2">
-        <v>126.06082191780823</v>
+        <v>122.30712328767122</v>
       </c>
       <c r="L48" s="2">
-        <v>0.4529619047619049</v>
+        <v>0.45233888888888857</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B49" s="1">
         <v>100</v>
       </c>
       <c r="C49" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
@@ -2391,19 +2391,19 @@
         <v>16</v>
       </c>
       <c r="H49">
-        <v>0.41499999999999998</v>
+        <v>0.44</v>
       </c>
       <c r="I49">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J49">
-        <v>30.698630136986299</v>
+        <v>32.547945205479458</v>
       </c>
       <c r="K49" s="2">
-        <v>133.31260273972603</v>
+        <v>133.21068493150685</v>
       </c>
       <c r="L49" s="2">
-        <v>0.45033703703703704</v>
+        <v>0.44895925925925922</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -2423,7 +2423,7 @@
         <v>12</v>
       </c>
       <c r="F50">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="G50" t="s">
         <v>16</v>
@@ -2435,13 +2435,13 @@
         <v>0.5</v>
       </c>
       <c r="J50">
-        <v>21.698630136986303</v>
+        <v>43.397260273972606</v>
       </c>
       <c r="K50" s="2">
-        <v>122.30712328767122</v>
+        <v>144.11424657534243</v>
       </c>
       <c r="L50" s="2">
-        <v>0.45233888888888857</v>
+        <v>0.44726944444444422</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -2452,7 +2452,7 @@
         <v>100</v>
       </c>
       <c r="C51" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
@@ -2461,25 +2461,25 @@
         <v>12</v>
       </c>
       <c r="F51">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="G51" t="s">
         <v>16</v>
       </c>
       <c r="H51">
-        <v>0.44</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="I51">
-        <v>0.5</v>
+        <v>5.2631578947368425</v>
       </c>
       <c r="J51">
-        <v>32.547945205479458</v>
+        <v>17.013698630136986</v>
       </c>
       <c r="K51" s="2">
-        <v>133.21068493150685</v>
+        <v>123.1723143475126</v>
       </c>
       <c r="L51" s="2">
-        <v>0.44895925925925922</v>
+        <v>0.46988304093567196</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -2490,7 +2490,7 @@
         <v>100</v>
       </c>
       <c r="C52" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
@@ -2499,25 +2499,25 @@
         <v>12</v>
       </c>
       <c r="F52">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="G52" t="s">
         <v>16</v>
       </c>
       <c r="H52">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="I52">
-        <v>0.5</v>
+        <v>5.2631578947368425</v>
       </c>
       <c r="J52">
-        <v>43.397260273972606</v>
+        <v>27.36986301369863</v>
       </c>
       <c r="K52" s="2">
-        <v>144.11424657534243</v>
+        <v>134.07354001441962</v>
       </c>
       <c r="L52" s="2">
-        <v>0.44726944444444422</v>
+        <v>0.46062378167641344</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -2537,25 +2537,25 @@
         <v>12</v>
       </c>
       <c r="F53">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="G53" t="s">
         <v>16</v>
       </c>
       <c r="H53">
-        <v>0.34499999999999997</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="I53">
         <v>5.2631578947368425</v>
       </c>
       <c r="J53">
-        <v>17.013698630136986</v>
+        <v>37.972602739726028</v>
       </c>
       <c r="K53" s="2">
-        <v>123.1723143475126</v>
+        <v>145.23431867339582</v>
       </c>
       <c r="L53" s="2">
-        <v>0.46988304093567196</v>
+        <v>0.45862573099415205</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -2566,7 +2566,7 @@
         <v>100</v>
       </c>
       <c r="C54" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
@@ -2575,25 +2575,25 @@
         <v>12</v>
       </c>
       <c r="F54">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="G54" t="s">
         <v>16</v>
       </c>
       <c r="H54">
-        <v>0.37</v>
+        <v>0.21</v>
       </c>
       <c r="I54">
-        <v>5.2631578947368425</v>
+        <v>11.111111111111112</v>
       </c>
       <c r="J54">
-        <v>27.36986301369863</v>
+        <v>10.356164383561643</v>
       </c>
       <c r="K54" s="2">
-        <v>134.07354001441962</v>
+        <v>122.61796042617961</v>
       </c>
       <c r="L54" s="2">
-        <v>0.46062378167641344</v>
+        <v>0.45864197530864198</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -2604,7 +2604,7 @@
         <v>100</v>
       </c>
       <c r="C55" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
@@ -2613,25 +2613,25 @@
         <v>12</v>
       </c>
       <c r="F55">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="G55" t="s">
         <v>16</v>
       </c>
       <c r="H55">
-        <v>0.38500000000000001</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I55">
-        <v>5.2631578947368425</v>
+        <v>11.111111111111112</v>
       </c>
       <c r="J55">
-        <v>37.972602739726028</v>
+        <v>20.712328767123289</v>
       </c>
       <c r="K55" s="2">
-        <v>145.23431867339582</v>
+        <v>134.1248097412481</v>
       </c>
       <c r="L55" s="2">
-        <v>0.45862573099415205</v>
+        <v>0.46131687242798353</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -2651,36 +2651,36 @@
         <v>12</v>
       </c>
       <c r="F56">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="G56" t="s">
         <v>16</v>
       </c>
       <c r="H56">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="I56">
         <v>11.111111111111112</v>
       </c>
       <c r="J56">
-        <v>10.356164383561643</v>
+        <v>30.575342465753426</v>
       </c>
       <c r="K56" s="2">
-        <v>122.61796042617961</v>
+        <v>145.08371385083714</v>
       </c>
       <c r="L56" s="2">
-        <v>0.45864197530864198</v>
+        <v>0.45709876543209876</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B57" s="1">
         <v>100</v>
       </c>
       <c r="C57" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -2689,36 +2689,36 @@
         <v>12</v>
       </c>
       <c r="F57">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="G57" t="s">
         <v>16</v>
       </c>
       <c r="H57">
-        <v>0.28000000000000003</v>
+        <v>0.21</v>
       </c>
       <c r="I57">
-        <v>11.111111111111112</v>
+        <v>10.9</v>
       </c>
       <c r="J57">
-        <v>20.712328767123289</v>
+        <v>10.356164383561643</v>
       </c>
       <c r="K57" s="2">
-        <v>134.1248097412481</v>
+        <v>122.38498630136986</v>
       </c>
       <c r="L57" s="2">
-        <v>0.46131687242798353</v>
+        <v>0.45391777777777786</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B58" s="1">
         <v>100</v>
       </c>
       <c r="C58" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
@@ -2727,25 +2727,25 @@
         <v>12</v>
       </c>
       <c r="F58">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="G58" t="s">
         <v>16</v>
       </c>
       <c r="H58">
-        <v>0.31</v>
+        <v>0.29499999999999998</v>
       </c>
       <c r="I58">
-        <v>11.111111111111112</v>
+        <v>10.9</v>
       </c>
       <c r="J58">
-        <v>30.575342465753426</v>
+        <v>21.82191780821918</v>
       </c>
       <c r="K58" s="2">
-        <v>145.08371385083714</v>
+        <v>135.10050684931508</v>
       </c>
       <c r="L58" s="2">
-        <v>0.45709876543209876</v>
+        <v>0.47450685185185187</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -2765,30 +2765,30 @@
         <v>12</v>
       </c>
       <c r="F59">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="G59" t="s">
         <v>16</v>
       </c>
       <c r="H59">
-        <v>0.21</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="I59">
         <v>10.9</v>
       </c>
       <c r="J59">
-        <v>10.356164383561643</v>
+        <v>34.027397260273972</v>
       </c>
       <c r="K59" s="2">
-        <v>122.38498630136986</v>
+        <v>148.63638356164384</v>
       </c>
       <c r="L59" s="2">
-        <v>0.45391777777777786</v>
+        <v>0.49311888888888888</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B60" s="1">
         <v>100</v>
@@ -2803,30 +2803,30 @@
         <v>12</v>
       </c>
       <c r="F60">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="G60" t="s">
         <v>16</v>
       </c>
       <c r="H60">
-        <v>0.29499999999999998</v>
+        <v>0.24</v>
       </c>
       <c r="I60">
         <v>10.9</v>
       </c>
       <c r="J60">
-        <v>21.82191780821918</v>
+        <v>11.835616438356164</v>
       </c>
       <c r="K60" s="2">
-        <v>135.10050684931508</v>
+        <v>124.02569863013699</v>
       </c>
       <c r="L60" s="2">
-        <v>0.47450685185185187</v>
+        <v>0.48718777777777794</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B61" s="1">
         <v>100</v>
@@ -2841,25 +2841,25 @@
         <v>12</v>
       </c>
       <c r="F61">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="G61" t="s">
         <v>16</v>
       </c>
       <c r="H61">
-        <v>0.34499999999999997</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="I61">
         <v>10.9</v>
       </c>
       <c r="J61">
-        <v>34.027397260273972</v>
+        <v>24.041095890410961</v>
       </c>
       <c r="K61" s="2">
-        <v>148.63638356164384</v>
+        <v>137.56157534246577</v>
       </c>
       <c r="L61" s="2">
-        <v>0.49311888888888888</v>
+        <v>0.50777685185185228</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -2879,101 +2879,101 @@
         <v>12</v>
       </c>
       <c r="F62">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="G62" t="s">
         <v>16</v>
       </c>
       <c r="H62">
-        <v>0.24</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="I62">
         <v>10.9</v>
       </c>
       <c r="J62">
-        <v>11.835616438356164</v>
+        <v>39.945205479452056</v>
       </c>
       <c r="K62" s="2">
-        <v>124.02569863013699</v>
+        <v>155.19923287671236</v>
       </c>
       <c r="L62" s="2">
-        <v>0.48718777777777794</v>
+        <v>0.55965888888888915</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B63" s="1">
         <v>100</v>
       </c>
       <c r="C63" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D63" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E63" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F63">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c r="G63" t="s">
         <v>16</v>
       </c>
       <c r="H63">
-        <v>0.32500000000000001</v>
+        <v>0</v>
       </c>
       <c r="I63">
-        <v>10.9</v>
+        <v>10.840572974123209</v>
       </c>
       <c r="J63">
-        <v>24.041095890410961</v>
+        <v>0</v>
       </c>
       <c r="K63" s="2">
-        <v>137.56157534246577</v>
+        <v>110.84057297412322</v>
       </c>
       <c r="L63" s="2">
-        <v>0.50777685185185228</v>
+        <v>0.65946818925916251</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B64" s="1">
         <v>100</v>
       </c>
       <c r="C64" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D64" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E64" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F64">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="G64" t="s">
         <v>16</v>
       </c>
       <c r="H64">
-        <v>0.40500000000000003</v>
+        <v>0</v>
       </c>
       <c r="I64">
-        <v>10.9</v>
+        <v>14.749401060857823</v>
       </c>
       <c r="J64">
-        <v>39.945205479452056</v>
+        <v>0</v>
       </c>
       <c r="K64" s="2">
-        <v>155.19923287671236</v>
+        <v>114.74940106085782</v>
       </c>
       <c r="L64" s="2">
-        <v>0.55965888888888915</v>
+        <v>0.59817015413478958</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -2993,7 +2993,7 @@
         <v>14</v>
       </c>
       <c r="F65">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G65" t="s">
         <v>16</v>
@@ -3002,16 +3002,16 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>12</v>
+        <v>18.664213926776743</v>
       </c>
       <c r="J65">
         <v>0</v>
       </c>
       <c r="K65" s="2">
-        <v>112.00000000000001</v>
+        <v>118.66421392677675</v>
       </c>
       <c r="L65" s="2">
-        <v>0.73000000000000065</v>
+        <v>0.56770317360612621</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3022,7 +3022,7 @@
         <v>100</v>
       </c>
       <c r="C66" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -3031,7 +3031,7 @@
         <v>14</v>
       </c>
       <c r="F66">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G66" t="s">
         <v>16</v>
@@ -3040,16 +3040,16 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J66">
         <v>0</v>
       </c>
       <c r="K66" s="2">
-        <v>117</v>
+        <v>110.00000000000001</v>
       </c>
       <c r="L66" s="2">
-        <v>0.68944444444444419</v>
+        <v>0.60833333333333384</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3060,7 +3060,7 @@
         <v>100</v>
       </c>
       <c r="C67" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -3069,7 +3069,7 @@
         <v>14</v>
       </c>
       <c r="F67">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G67" t="s">
         <v>16</v>
@@ -3078,16 +3078,16 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>21</v>
+        <v>14.000000000000002</v>
       </c>
       <c r="J67">
         <v>0</v>
       </c>
       <c r="K67" s="2">
-        <v>121</v>
+        <v>114.00000000000001</v>
       </c>
       <c r="L67" s="2">
-        <v>0.63874999999999982</v>
+        <v>0.56777777777777827</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -3107,7 +3107,7 @@
         <v>14</v>
       </c>
       <c r="F68">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G68" t="s">
         <v>16</v>
@@ -3116,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J68">
         <v>0</v>
       </c>
       <c r="K68" s="2">
-        <v>110.00000000000001</v>
+        <v>118</v>
       </c>
       <c r="L68" s="2">
-        <v>0.60833333333333384</v>
+        <v>0.54749999999999976</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3145,7 +3145,7 @@
         <v>14</v>
       </c>
       <c r="F69">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="G69" t="s">
         <v>16</v>
@@ -3154,16 +3154,16 @@
         <v>0</v>
       </c>
       <c r="I69">
-        <v>14.000000000000002</v>
+        <v>23</v>
       </c>
       <c r="J69">
         <v>0</v>
       </c>
       <c r="K69" s="2">
-        <v>114.00000000000001</v>
+        <v>123</v>
       </c>
       <c r="L69" s="2">
-        <v>0.56777777777777827</v>
+        <v>0.55966666666666665</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -3183,7 +3183,7 @@
         <v>14</v>
       </c>
       <c r="F70">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G70" t="s">
         <v>16</v>
@@ -3192,16 +3192,16 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>18</v>
+        <v>28.000000000000004</v>
       </c>
       <c r="J70">
         <v>0</v>
       </c>
       <c r="K70" s="2">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L70" s="2">
-        <v>0.54749999999999976</v>
+        <v>0.56777777777777783</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -3212,7 +3212,7 @@
         <v>100</v>
       </c>
       <c r="C71" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -3221,7 +3221,7 @@
         <v>14</v>
       </c>
       <c r="F71">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G71" t="s">
         <v>16</v>
@@ -3230,16 +3230,16 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J71">
         <v>0</v>
       </c>
       <c r="K71" s="2">
-        <v>123</v>
+        <v>109.00000000000001</v>
       </c>
       <c r="L71" s="2">
-        <v>0.55966666666666665</v>
+        <v>0.54750000000000054</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -3250,7 +3250,7 @@
         <v>100</v>
       </c>
       <c r="C72" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -3259,7 +3259,7 @@
         <v>14</v>
       </c>
       <c r="F72">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G72" t="s">
         <v>16</v>
@@ -3268,16 +3268,16 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>28.000000000000004</v>
+        <v>12</v>
       </c>
       <c r="J72">
         <v>0</v>
       </c>
       <c r="K72" s="2">
-        <v>128</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="L72" s="2">
-        <v>0.56777777777777783</v>
+        <v>0.48666666666666714</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -3297,7 +3297,7 @@
         <v>14</v>
       </c>
       <c r="F73">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G73" t="s">
         <v>16</v>
@@ -3306,16 +3306,16 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J73">
         <v>0</v>
       </c>
       <c r="K73" s="2">
-        <v>109.00000000000001</v>
+        <v>115.99999999999999</v>
       </c>
       <c r="L73" s="2">
-        <v>0.54750000000000054</v>
+        <v>0.48666666666666641</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -3335,7 +3335,7 @@
         <v>14</v>
       </c>
       <c r="F74">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="G74" t="s">
         <v>16</v>
@@ -3344,16 +3344,16 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J74">
         <v>0</v>
       </c>
       <c r="K74" s="2">
-        <v>112.00000000000001</v>
+        <v>120</v>
       </c>
       <c r="L74" s="2">
-        <v>0.48666666666666714</v>
+        <v>0.48666666666666658</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -3373,7 +3373,7 @@
         <v>14</v>
       </c>
       <c r="F75">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G75" t="s">
         <v>16</v>
@@ -3382,16 +3382,16 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J75">
         <v>0</v>
       </c>
       <c r="K75" s="2">
-        <v>115.99999999999999</v>
+        <v>124</v>
       </c>
       <c r="L75" s="2">
-        <v>0.48666666666666641</v>
+        <v>0.48666666666666664</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -3402,7 +3402,7 @@
         <v>100</v>
       </c>
       <c r="C76" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D76" t="s">
         <v>19</v>
@@ -3411,7 +3411,7 @@
         <v>14</v>
       </c>
       <c r="F76">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G76" t="s">
         <v>16</v>
@@ -3420,16 +3420,16 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J76">
         <v>0</v>
       </c>
       <c r="K76" s="2">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="L76" s="2">
-        <v>0.48666666666666658</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -3440,7 +3440,7 @@
         <v>100</v>
       </c>
       <c r="C77" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D77" t="s">
         <v>19</v>
@@ -3449,7 +3449,7 @@
         <v>14</v>
       </c>
       <c r="F77">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G77" t="s">
         <v>16</v>
@@ -3458,16 +3458,16 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J77">
         <v>0</v>
       </c>
       <c r="K77" s="2">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="L77" s="2">
-        <v>0.48666666666666664</v>
+        <v>0.32444444444444476</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -3487,7 +3487,7 @@
         <v>14</v>
       </c>
       <c r="F78">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G78" t="s">
         <v>16</v>
@@ -3496,13 +3496,13 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J78">
         <v>0</v>
       </c>
       <c r="K78" s="2">
-        <v>106</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="L78" s="2">
         <v>0.36500000000000032</v>
@@ -3525,7 +3525,7 @@
         <v>14</v>
       </c>
       <c r="F79">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="G79" t="s">
         <v>16</v>
@@ -3534,16 +3534,16 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J79">
         <v>0</v>
       </c>
       <c r="K79" s="2">
-        <v>108</v>
+        <v>114.99999999999999</v>
       </c>
       <c r="L79" s="2">
-        <v>0.32444444444444476</v>
+        <v>0.36499999999999977</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -3563,7 +3563,7 @@
         <v>14</v>
       </c>
       <c r="F80">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G80" t="s">
         <v>16</v>
@@ -3572,16 +3572,16 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J80">
         <v>0</v>
       </c>
       <c r="K80" s="2">
-        <v>112.00000000000001</v>
+        <v>118</v>
       </c>
       <c r="L80" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.36499999999999982</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -3592,7 +3592,7 @@
         <v>100</v>
       </c>
       <c r="C81" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D81" t="s">
         <v>19</v>
@@ -3601,7 +3601,7 @@
         <v>14</v>
       </c>
       <c r="F81">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G81" t="s">
         <v>16</v>
@@ -3610,16 +3610,16 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81" s="2">
-        <v>114.99999999999999</v>
+        <v>106</v>
       </c>
       <c r="L81" s="2">
-        <v>0.36499999999999977</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -3630,7 +3630,7 @@
         <v>100</v>
       </c>
       <c r="C82" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D82" t="s">
         <v>19</v>
@@ -3639,7 +3639,7 @@
         <v>14</v>
       </c>
       <c r="F82">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G82" t="s">
         <v>16</v>
@@ -3648,16 +3648,16 @@
         <v>0</v>
       </c>
       <c r="I82">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J82">
         <v>0</v>
       </c>
       <c r="K82" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="L82" s="2">
-        <v>0.36499999999999982</v>
+        <v>0.32444444444444476</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -3677,7 +3677,7 @@
         <v>14</v>
       </c>
       <c r="F83">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G83" t="s">
         <v>16</v>
@@ -3686,13 +3686,13 @@
         <v>0</v>
       </c>
       <c r="I83">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J83">
         <v>0</v>
       </c>
       <c r="K83" s="2">
-        <v>106</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="L83" s="2">
         <v>0.36500000000000032</v>
@@ -3715,7 +3715,7 @@
         <v>14</v>
       </c>
       <c r="F84">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="G84" t="s">
         <v>16</v>
@@ -3724,16 +3724,16 @@
         <v>0</v>
       </c>
       <c r="I84">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J84">
         <v>0</v>
       </c>
       <c r="K84" s="2">
-        <v>108</v>
+        <v>114.99999999999999</v>
       </c>
       <c r="L84" s="2">
-        <v>0.32444444444444476</v>
+        <v>0.36499999999999977</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -3753,7 +3753,7 @@
         <v>14</v>
       </c>
       <c r="F85">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G85" t="s">
         <v>16</v>
@@ -3762,16 +3762,16 @@
         <v>0</v>
       </c>
       <c r="I85">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J85">
         <v>0</v>
       </c>
       <c r="K85" s="2">
-        <v>112.00000000000001</v>
+        <v>118</v>
       </c>
       <c r="L85" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.36499999999999982</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -3782,7 +3782,7 @@
         <v>100</v>
       </c>
       <c r="C86" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D86" t="s">
         <v>19</v>
@@ -3791,7 +3791,7 @@
         <v>14</v>
       </c>
       <c r="F86">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G86" t="s">
         <v>16</v>
@@ -3800,16 +3800,16 @@
         <v>0</v>
       </c>
       <c r="I86">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86" s="2">
-        <v>114.99999999999999</v>
+        <v>106</v>
       </c>
       <c r="L86" s="2">
-        <v>0.36499999999999977</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -3820,7 +3820,7 @@
         <v>100</v>
       </c>
       <c r="C87" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D87" t="s">
         <v>19</v>
@@ -3829,7 +3829,7 @@
         <v>14</v>
       </c>
       <c r="F87">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G87" t="s">
         <v>16</v>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J87">
         <v>0</v>
       </c>
       <c r="K87" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="L87" s="2">
-        <v>0.36499999999999982</v>
+        <v>0.32444444444444476</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -3867,7 +3867,7 @@
         <v>14</v>
       </c>
       <c r="F88">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G88" t="s">
         <v>16</v>
@@ -3876,13 +3876,13 @@
         <v>0</v>
       </c>
       <c r="I88">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J88">
         <v>0</v>
       </c>
       <c r="K88" s="2">
-        <v>106</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="L88" s="2">
         <v>0.36500000000000032</v>
@@ -3905,7 +3905,7 @@
         <v>14</v>
       </c>
       <c r="F89">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="G89" t="s">
         <v>16</v>
@@ -3914,16 +3914,16 @@
         <v>0</v>
       </c>
       <c r="I89">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J89">
         <v>0</v>
       </c>
       <c r="K89" s="2">
-        <v>108</v>
+        <v>114.99999999999999</v>
       </c>
       <c r="L89" s="2">
-        <v>0.32444444444444476</v>
+        <v>0.36499999999999977</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -3943,7 +3943,7 @@
         <v>14</v>
       </c>
       <c r="F90">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G90" t="s">
         <v>16</v>
@@ -3952,16 +3952,16 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J90">
         <v>0</v>
       </c>
       <c r="K90" s="2">
-        <v>112.00000000000001</v>
+        <v>118</v>
       </c>
       <c r="L90" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.36499999999999982</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -3972,7 +3972,7 @@
         <v>100</v>
       </c>
       <c r="C91" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D91" t="s">
         <v>19</v>
@@ -3981,7 +3981,7 @@
         <v>14</v>
       </c>
       <c r="F91">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G91" t="s">
         <v>16</v>
@@ -3990,16 +3990,16 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J91">
         <v>0</v>
       </c>
       <c r="K91" s="2">
-        <v>114.99999999999999</v>
+        <v>106</v>
       </c>
       <c r="L91" s="2">
-        <v>0.36499999999999977</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4010,7 +4010,7 @@
         <v>100</v>
       </c>
       <c r="C92" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D92" t="s">
         <v>19</v>
@@ -4019,7 +4019,7 @@
         <v>14</v>
       </c>
       <c r="F92">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G92" t="s">
         <v>16</v>
@@ -4028,16 +4028,16 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J92">
         <v>0</v>
       </c>
       <c r="K92" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="L92" s="2">
-        <v>0.36499999999999982</v>
+        <v>0.32444444444444476</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -4057,7 +4057,7 @@
         <v>14</v>
       </c>
       <c r="F93">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G93" t="s">
         <v>16</v>
@@ -4066,13 +4066,13 @@
         <v>0</v>
       </c>
       <c r="I93">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J93">
         <v>0</v>
       </c>
       <c r="K93" s="2">
-        <v>106</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="L93" s="2">
         <v>0.36500000000000032</v>
@@ -4095,7 +4095,7 @@
         <v>14</v>
       </c>
       <c r="F94">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="G94" t="s">
         <v>16</v>
@@ -4104,16 +4104,16 @@
         <v>0</v>
       </c>
       <c r="I94">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J94">
         <v>0</v>
       </c>
       <c r="K94" s="2">
-        <v>108</v>
+        <v>114.99999999999999</v>
       </c>
       <c r="L94" s="2">
-        <v>0.32444444444444476</v>
+        <v>0.36499999999999977</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4133,7 +4133,7 @@
         <v>14</v>
       </c>
       <c r="F95">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G95" t="s">
         <v>16</v>
@@ -4142,16 +4142,16 @@
         <v>0</v>
       </c>
       <c r="I95">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J95">
         <v>0</v>
       </c>
       <c r="K95" s="2">
-        <v>112.00000000000001</v>
+        <v>118</v>
       </c>
       <c r="L95" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.36499999999999982</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -4162,7 +4162,7 @@
         <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D96" t="s">
         <v>19</v>
@@ -4171,7 +4171,7 @@
         <v>14</v>
       </c>
       <c r="F96">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G96" t="s">
         <v>16</v>
@@ -4180,16 +4180,16 @@
         <v>0</v>
       </c>
       <c r="I96">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J96">
         <v>0</v>
       </c>
       <c r="K96" s="2">
-        <v>114.99999999999999</v>
+        <v>106</v>
       </c>
       <c r="L96" s="2">
-        <v>0.36499999999999977</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4200,7 +4200,7 @@
         <v>100</v>
       </c>
       <c r="C97" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D97" t="s">
         <v>19</v>
@@ -4209,7 +4209,7 @@
         <v>14</v>
       </c>
       <c r="F97">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G97" t="s">
         <v>16</v>
@@ -4218,16 +4218,16 @@
         <v>0</v>
       </c>
       <c r="I97">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J97">
         <v>0</v>
       </c>
       <c r="K97" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="L97" s="2">
-        <v>0.36499999999999982</v>
+        <v>0.32444444444444476</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4247,7 +4247,7 @@
         <v>14</v>
       </c>
       <c r="F98">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G98" t="s">
         <v>16</v>
@@ -4256,13 +4256,13 @@
         <v>0</v>
       </c>
       <c r="I98">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J98">
         <v>0</v>
       </c>
       <c r="K98" s="2">
-        <v>106</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="L98" s="2">
         <v>0.36500000000000032</v>
@@ -4285,7 +4285,7 @@
         <v>14</v>
       </c>
       <c r="F99">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="G99" t="s">
         <v>16</v>
@@ -4294,16 +4294,16 @@
         <v>0</v>
       </c>
       <c r="I99">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J99">
         <v>0</v>
       </c>
       <c r="K99" s="2">
-        <v>108</v>
+        <v>114.99999999999999</v>
       </c>
       <c r="L99" s="2">
-        <v>0.32444444444444476</v>
+        <v>0.36499999999999977</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4323,7 +4323,7 @@
         <v>14</v>
       </c>
       <c r="F100">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G100" t="s">
         <v>16</v>
@@ -4332,16 +4332,16 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J100">
         <v>0</v>
       </c>
       <c r="K100" s="2">
-        <v>112.00000000000001</v>
+        <v>118</v>
       </c>
       <c r="L100" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.36499999999999982</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4352,7 +4352,7 @@
         <v>100</v>
       </c>
       <c r="C101" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D101" t="s">
         <v>19</v>
@@ -4361,7 +4361,7 @@
         <v>14</v>
       </c>
       <c r="F101">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G101" t="s">
         <v>16</v>
@@ -4370,16 +4370,16 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J101">
         <v>0</v>
       </c>
       <c r="K101" s="2">
-        <v>114.99999999999999</v>
+        <v>106</v>
       </c>
       <c r="L101" s="2">
-        <v>0.36499999999999977</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4390,7 +4390,7 @@
         <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D102" t="s">
         <v>19</v>
@@ -4399,7 +4399,7 @@
         <v>14</v>
       </c>
       <c r="F102">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G102" t="s">
         <v>16</v>
@@ -4408,16 +4408,16 @@
         <v>0</v>
       </c>
       <c r="I102">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J102">
         <v>0</v>
       </c>
       <c r="K102" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="L102" s="2">
-        <v>0.36499999999999982</v>
+        <v>0.32444444444444476</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4437,7 +4437,7 @@
         <v>14</v>
       </c>
       <c r="F103">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G103" t="s">
         <v>16</v>
@@ -4446,13 +4446,13 @@
         <v>0</v>
       </c>
       <c r="I103">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J103">
         <v>0</v>
       </c>
       <c r="K103" s="2">
-        <v>106</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="L103" s="2">
         <v>0.36500000000000032</v>
@@ -4475,7 +4475,7 @@
         <v>14</v>
       </c>
       <c r="F104">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="G104" t="s">
         <v>16</v>
@@ -4484,16 +4484,16 @@
         <v>0</v>
       </c>
       <c r="I104">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J104">
         <v>0</v>
       </c>
       <c r="K104" s="2">
-        <v>108</v>
+        <v>114.99999999999999</v>
       </c>
       <c r="L104" s="2">
-        <v>0.32444444444444476</v>
+        <v>0.36499999999999977</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -4513,7 +4513,7 @@
         <v>14</v>
       </c>
       <c r="F105">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G105" t="s">
         <v>16</v>
@@ -4522,16 +4522,16 @@
         <v>0</v>
       </c>
       <c r="I105">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J105">
         <v>0</v>
       </c>
       <c r="K105" s="2">
-        <v>112.00000000000001</v>
+        <v>118</v>
       </c>
       <c r="L105" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.36499999999999982</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -4542,7 +4542,7 @@
         <v>100</v>
       </c>
       <c r="C106" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D106" t="s">
         <v>19</v>
@@ -4551,7 +4551,7 @@
         <v>14</v>
       </c>
       <c r="F106">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G106" t="s">
         <v>16</v>
@@ -4560,16 +4560,16 @@
         <v>0</v>
       </c>
       <c r="I106">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J106">
         <v>0</v>
       </c>
       <c r="K106" s="2">
-        <v>114.99999999999999</v>
+        <v>106</v>
       </c>
       <c r="L106" s="2">
-        <v>0.36499999999999977</v>
+        <v>0.36500000000000032</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -4580,7 +4580,7 @@
         <v>100</v>
       </c>
       <c r="C107" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D107" t="s">
         <v>19</v>
@@ -4589,7 +4589,7 @@
         <v>14</v>
       </c>
       <c r="F107">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G107" t="s">
         <v>16</v>
@@ -4598,16 +4598,16 @@
         <v>0</v>
       </c>
       <c r="I107">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J107">
         <v>0</v>
       </c>
       <c r="K107" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="L107" s="2">
-        <v>0.36499999999999982</v>
+        <v>0.32444444444444476</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -4627,7 +4627,7 @@
         <v>14</v>
       </c>
       <c r="F108">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G108" t="s">
         <v>16</v>
@@ -4636,13 +4636,13 @@
         <v>0</v>
       </c>
       <c r="I108">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J108">
         <v>0</v>
       </c>
       <c r="K108" s="2">
-        <v>106</v>
+        <v>112.00000000000001</v>
       </c>
       <c r="L108" s="2">
         <v>0.36500000000000032</v>
@@ -4665,7 +4665,7 @@
         <v>14</v>
       </c>
       <c r="F109">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="G109" t="s">
         <v>16</v>
@@ -4674,16 +4674,16 @@
         <v>0</v>
       </c>
       <c r="I109">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J109">
         <v>0</v>
       </c>
       <c r="K109" s="2">
-        <v>108</v>
+        <v>114.99999999999999</v>
       </c>
       <c r="L109" s="2">
-        <v>0.32444444444444476</v>
+        <v>0.36499999999999977</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -4703,7 +4703,7 @@
         <v>14</v>
       </c>
       <c r="F110">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G110" t="s">
         <v>16</v>
@@ -4712,16 +4712,16 @@
         <v>0</v>
       </c>
       <c r="I110">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J110">
         <v>0</v>
       </c>
       <c r="K110" s="2">
-        <v>112.00000000000001</v>
+        <v>118</v>
       </c>
       <c r="L110" s="2">
-        <v>0.36500000000000032</v>
+        <v>0.36499999999999982</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -4732,34 +4732,34 @@
         <v>100</v>
       </c>
       <c r="C111" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D111" t="s">
         <v>19</v>
       </c>
       <c r="E111" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F111">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G111" t="s">
         <v>16</v>
       </c>
       <c r="H111">
-        <v>0</v>
+        <v>0.39137800925925947</v>
       </c>
       <c r="I111">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J111">
-        <v>0</v>
+        <v>6.4336111111111149</v>
       </c>
       <c r="K111" s="2">
-        <v>114.99999999999999</v>
+        <v>108.56228333333334</v>
       </c>
       <c r="L111" s="2">
-        <v>0.36499999999999977</v>
+        <v>0.520872236111111</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -4770,34 +4770,34 @@
         <v>100</v>
       </c>
       <c r="C112" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D112" t="s">
         <v>19</v>
       </c>
       <c r="E112" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F112">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G112" t="s">
         <v>16</v>
       </c>
       <c r="H112">
-        <v>0</v>
+        <v>0.39760702340535009</v>
       </c>
       <c r="I112">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J112">
-        <v>0</v>
+        <v>9.804008796296305</v>
       </c>
       <c r="K112" s="2">
-        <v>118</v>
+        <v>112.00008897222223</v>
       </c>
       <c r="L112" s="2">
-        <v>0.36499999999999982</v>
+        <v>0.48667027498456789</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -4817,25 +4817,25 @@
         <v>27</v>
       </c>
       <c r="F113">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="G113" t="s">
         <v>16</v>
       </c>
       <c r="H113">
-        <v>0.39137800925925947</v>
+        <v>0.41709773718002596</v>
       </c>
       <c r="I113">
         <v>2</v>
       </c>
       <c r="J113">
-        <v>6.4336111111111149</v>
+        <v>20.569203477371147</v>
       </c>
       <c r="K113" s="2">
-        <v>108.56228333333334</v>
+        <v>122.98058754691857</v>
       </c>
       <c r="L113" s="2">
-        <v>0.520872236111111</v>
+        <v>0.46599524747918197</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -4855,25 +4855,25 @@
         <v>27</v>
       </c>
       <c r="F114">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="G114" t="s">
         <v>16</v>
       </c>
       <c r="H114">
-        <v>0.39760702340535009</v>
+        <v>0.50397751875154939</v>
       </c>
       <c r="I114">
         <v>2</v>
       </c>
       <c r="J114">
-        <v>9.804008796296305</v>
+        <v>37.280528784361188</v>
       </c>
       <c r="K114" s="2">
-        <v>112.00008897222223</v>
+        <v>140.0261393600484</v>
       </c>
       <c r="L114" s="2">
-        <v>0.48667027498456789</v>
+        <v>0.54109410616361719</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -4893,25 +4893,25 @@
         <v>27</v>
       </c>
       <c r="F115">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="G115" t="s">
         <v>16</v>
       </c>
       <c r="H115">
-        <v>0.41709773718002596</v>
+        <v>0.53303503052700441</v>
       </c>
       <c r="I115">
         <v>2</v>
       </c>
       <c r="J115">
-        <v>20.569203477371147</v>
+        <v>52.573318079375774</v>
       </c>
       <c r="K115" s="2">
-        <v>122.98058754691857</v>
+        <v>155.62478444096328</v>
       </c>
       <c r="L115" s="2">
-        <v>0.46599524747918197</v>
+        <v>0.56397350891532216</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -4922,7 +4922,7 @@
         <v>100</v>
       </c>
       <c r="C116" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D116" t="s">
         <v>19</v>
@@ -4931,25 +4931,25 @@
         <v>27</v>
       </c>
       <c r="F116">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c r="G116" t="s">
         <v>16</v>
       </c>
       <c r="H116">
-        <v>0.50397751875154939</v>
+        <v>0.44</v>
       </c>
       <c r="I116">
         <v>2</v>
       </c>
       <c r="J116">
-        <v>37.280528784361188</v>
+        <v>7.2328767123287676</v>
       </c>
       <c r="K116" s="2">
-        <v>140.0261393600484</v>
+        <v>109.37753424657535</v>
       </c>
       <c r="L116" s="2">
-        <v>0.54109410616361719</v>
+        <v>0.57046666666666701</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -4960,7 +4960,7 @@
         <v>100</v>
       </c>
       <c r="C117" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D117" t="s">
         <v>19</v>
@@ -4969,25 +4969,25 @@
         <v>27</v>
       </c>
       <c r="F117">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="G117" t="s">
         <v>16</v>
       </c>
       <c r="H117">
-        <v>0.53303503052700441</v>
+        <v>0.44</v>
       </c>
       <c r="I117">
         <v>2</v>
       </c>
       <c r="J117">
-        <v>52.573318079375774</v>
+        <v>10.849315068493151</v>
       </c>
       <c r="K117" s="2">
-        <v>155.62478444096328</v>
+        <v>113.06630136986303</v>
       </c>
       <c r="L117" s="2">
-        <v>0.56397350891532216</v>
+        <v>0.52991111111111133</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -5007,7 +5007,7 @@
         <v>27</v>
       </c>
       <c r="F118">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="G118" t="s">
         <v>16</v>
@@ -5019,13 +5019,13 @@
         <v>2</v>
       </c>
       <c r="J118">
-        <v>7.2328767123287676</v>
+        <v>21.698630136986303</v>
       </c>
       <c r="K118" s="2">
-        <v>109.37753424657535</v>
+        <v>124.13260273972602</v>
       </c>
       <c r="L118" s="2">
-        <v>0.57046666666666701</v>
+        <v>0.48935555555555532</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -5045,7 +5045,7 @@
         <v>27</v>
       </c>
       <c r="F119">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="G119" t="s">
         <v>16</v>
@@ -5057,13 +5057,13 @@
         <v>2</v>
       </c>
       <c r="J119">
-        <v>10.849315068493151</v>
+        <v>32.547945205479458</v>
       </c>
       <c r="K119" s="2">
-        <v>113.06630136986303</v>
+        <v>135.19890410958905</v>
       </c>
       <c r="L119" s="2">
-        <v>0.52991111111111133</v>
+        <v>0.47583703703703728</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -5083,7 +5083,7 @@
         <v>27</v>
       </c>
       <c r="F120">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="G120" t="s">
         <v>16</v>
@@ -5095,13 +5095,13 @@
         <v>2</v>
       </c>
       <c r="J120">
-        <v>21.698630136986303</v>
+        <v>43.397260273972606</v>
       </c>
       <c r="K120" s="2">
-        <v>124.13260273972602</v>
+        <v>146.26520547945205</v>
       </c>
       <c r="L120" s="2">
-        <v>0.48935555555555532</v>
+        <v>0.46907777777777776</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -5112,7 +5112,7 @@
         <v>100</v>
       </c>
       <c r="C121" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D121" t="s">
         <v>19</v>
@@ -5121,25 +5121,25 @@
         <v>27</v>
       </c>
       <c r="F121">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c r="G121" t="s">
         <v>16</v>
       </c>
       <c r="H121">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="I121">
         <v>2</v>
       </c>
       <c r="J121">
-        <v>32.547945205479458</v>
+        <v>5.2602739726027403</v>
       </c>
       <c r="K121" s="2">
-        <v>135.19890410958905</v>
+        <v>107.36547945205479</v>
       </c>
       <c r="L121" s="2">
-        <v>0.47583703703703728</v>
+        <v>0.44806666666666639</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -5150,7 +5150,7 @@
         <v>100</v>
       </c>
       <c r="C122" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D122" t="s">
         <v>19</v>
@@ -5159,25 +5159,25 @@
         <v>27</v>
       </c>
       <c r="F122">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="G122" t="s">
         <v>16</v>
       </c>
       <c r="H122">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="I122">
         <v>2</v>
       </c>
       <c r="J122">
-        <v>43.397260273972606</v>
+        <v>7.8904109589041092</v>
       </c>
       <c r="K122" s="2">
-        <v>146.26520547945205</v>
+        <v>110.04821917808219</v>
       </c>
       <c r="L122" s="2">
-        <v>0.46907777777777776</v>
+        <v>0.40751111111111088</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -5197,25 +5197,25 @@
         <v>27</v>
       </c>
       <c r="F123">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="G123" t="s">
         <v>16</v>
       </c>
       <c r="H123">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="I123">
         <v>2</v>
       </c>
       <c r="J123">
-        <v>5.0958904109589049</v>
+        <v>15.780821917808218</v>
       </c>
       <c r="K123" s="2">
-        <v>107.19780821917809</v>
+        <v>118.09643835616437</v>
       </c>
       <c r="L123" s="2">
-        <v>0.43786666666666657</v>
+        <v>0.3669555555555552</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -5235,25 +5235,25 @@
         <v>27</v>
       </c>
       <c r="F124">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="G124" t="s">
         <v>16</v>
       </c>
       <c r="H124">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="I124">
         <v>2</v>
       </c>
       <c r="J124">
-        <v>7.6438356164383565</v>
+        <v>23.671232876712327</v>
       </c>
       <c r="K124" s="2">
-        <v>109.79671232876713</v>
+        <v>126.14465753424658</v>
       </c>
       <c r="L124" s="2">
-        <v>0.39731111111111145</v>
+        <v>0.35343703703703705</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -5273,25 +5273,25 @@
         <v>27</v>
       </c>
       <c r="F125">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="G125" t="s">
         <v>16</v>
       </c>
       <c r="H125">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="I125">
         <v>2</v>
       </c>
       <c r="J125">
-        <v>15.287671232876713</v>
+        <v>31.561643835616437</v>
       </c>
       <c r="K125" s="2">
-        <v>117.59342465753424</v>
+        <v>134.19287671232877</v>
       </c>
       <c r="L125" s="2">
-        <v>0.35675555555555544</v>
+        <v>0.34667777777777786</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -5302,7 +5302,7 @@
         <v>100</v>
       </c>
       <c r="C126" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D126" t="s">
         <v>19</v>
@@ -5311,25 +5311,25 @@
         <v>27</v>
       </c>
       <c r="F126">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c r="G126" t="s">
         <v>16</v>
       </c>
       <c r="H126">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
       <c r="I126">
         <v>2</v>
       </c>
       <c r="J126">
-        <v>22.93150684931507</v>
+        <v>7.0684931506849322</v>
       </c>
       <c r="K126" s="2">
-        <v>125.39013698630137</v>
+        <v>109.20986301369864</v>
       </c>
       <c r="L126" s="2">
-        <v>0.34323703703703701</v>
+        <v>0.56026666666666713</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -5340,7 +5340,7 @@
         <v>100</v>
       </c>
       <c r="C127" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D127" t="s">
         <v>19</v>
@@ -5349,25 +5349,25 @@
         <v>27</v>
       </c>
       <c r="F127">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="G127" t="s">
         <v>16</v>
       </c>
       <c r="H127">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
       <c r="I127">
         <v>2</v>
       </c>
       <c r="J127">
-        <v>30.575342465753426</v>
+        <v>10.602739726027398</v>
       </c>
       <c r="K127" s="2">
-        <v>133.18684931506849</v>
+        <v>112.81479452054793</v>
       </c>
       <c r="L127" s="2">
-        <v>0.3364777777777776</v>
+        <v>0.51971111111111112</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -5387,25 +5387,25 @@
         <v>27</v>
       </c>
       <c r="F128">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="G128" t="s">
         <v>16</v>
       </c>
       <c r="H128">
-        <v>0.42499999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="I128">
         <v>2</v>
       </c>
       <c r="J128">
-        <v>6.9863013698630123</v>
+        <v>21.205479452054796</v>
       </c>
       <c r="K128" s="2">
-        <v>109.12602739726026</v>
+        <v>123.6295890410959</v>
       </c>
       <c r="L128" s="2">
-        <v>0.55516666666666514</v>
+        <v>0.47915555555555556</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -5425,25 +5425,25 @@
         <v>27</v>
       </c>
       <c r="F129">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="G129" t="s">
         <v>16</v>
       </c>
       <c r="H129">
-        <v>0.42499999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="I129">
         <v>2</v>
       </c>
       <c r="J129">
-        <v>10.479452054794521</v>
+        <v>31.808219178082194</v>
       </c>
       <c r="K129" s="2">
-        <v>112.68904109589042</v>
+        <v>134.44438356164383</v>
       </c>
       <c r="L129" s="2">
-        <v>0.51461111111111146</v>
+        <v>0.46563703703703702</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -5463,101 +5463,25 @@
         <v>27</v>
       </c>
       <c r="F130">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="G130" t="s">
         <v>16</v>
       </c>
       <c r="H130">
-        <v>0.42499999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="I130">
         <v>2</v>
       </c>
       <c r="J130">
-        <v>20.958904109589042</v>
+        <v>42.410958904109592</v>
       </c>
       <c r="K130" s="2">
-        <v>123.37808219178083</v>
+        <v>145.2591780821918</v>
       </c>
       <c r="L130" s="2">
-        <v>0.47405555555555584</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>33</v>
-      </c>
-      <c r="B131" s="1">
-        <v>100</v>
-      </c>
-      <c r="C131" t="s">
-        <v>29</v>
-      </c>
-      <c r="D131" t="s">
-        <v>19</v>
-      </c>
-      <c r="E131" t="s">
-        <v>27</v>
-      </c>
-      <c r="F131">
-        <v>270</v>
-      </c>
-      <c r="G131" t="s">
-        <v>16</v>
-      </c>
-      <c r="H131">
-        <v>0.42499999999999999</v>
-      </c>
-      <c r="I131">
-        <v>2</v>
-      </c>
-      <c r="J131">
-        <v>31.438356164383556</v>
-      </c>
-      <c r="K131" s="2">
-        <v>134.06712328767122</v>
-      </c>
-      <c r="L131" s="2">
-        <v>0.46053703703703697</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>33</v>
-      </c>
-      <c r="B132" s="1">
-        <v>100</v>
-      </c>
-      <c r="C132" t="s">
-        <v>29</v>
-      </c>
-      <c r="D132" t="s">
-        <v>19</v>
-      </c>
-      <c r="E132" t="s">
-        <v>27</v>
-      </c>
-      <c r="F132">
-        <v>360</v>
-      </c>
-      <c r="G132" t="s">
-        <v>16</v>
-      </c>
-      <c r="H132">
-        <v>0.42499999999999999</v>
-      </c>
-      <c r="I132">
-        <v>2</v>
-      </c>
-      <c r="J132">
-        <v>41.917808219178085</v>
-      </c>
-      <c r="K132" s="2">
-        <v>144.75616438356164</v>
-      </c>
-      <c r="L132" s="2">
-        <v>0.45377777777777778</v>
+        <v>0.45887777777777794</v>
       </c>
     </row>
   </sheetData>

--- a/public/datos.xlsx
+++ b/public/datos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Financiera\Gestion Financiera\Condiciones Comerciales - Convenios Tarjetas\Simulador online\simulador ok\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NicolasAcebo\OneDrive - LARTIRIGOYEN Y CIA. S.A\Escritorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB08C33-99FE-4009-9DBB-A5E8CFB2ED99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9F2405-5A48-4255-A7CC-62A770280A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5F5C8F4A-A9C3-4394-B81C-80D194F2AEAA}"/>
   </bookViews>
@@ -2695,19 +2695,19 @@
         <v>16</v>
       </c>
       <c r="H57">
-        <v>0.21</v>
+        <v>0.155</v>
       </c>
       <c r="I57">
         <v>10.9</v>
       </c>
       <c r="J57">
-        <v>10.356164383561643</v>
+        <v>7.6438356164383565</v>
       </c>
       <c r="K57" s="2">
-        <v>122.38498630136986</v>
+        <v>119.37701369863014</v>
       </c>
       <c r="L57" s="2">
-        <v>0.45391777777777786</v>
+        <v>0.39292277777777784</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -2733,19 +2733,19 @@
         <v>16</v>
       </c>
       <c r="H58">
-        <v>0.29499999999999998</v>
+        <v>0.24</v>
       </c>
       <c r="I58">
         <v>10.9</v>
       </c>
       <c r="J58">
-        <v>21.82191780821918</v>
+        <v>17.753424657534246</v>
       </c>
       <c r="K58" s="2">
-        <v>135.10050684931508</v>
+        <v>130.58854794520548</v>
       </c>
       <c r="L58" s="2">
-        <v>0.47450685185185187</v>
+        <v>0.41351185185185169</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -2771,19 +2771,19 @@
         <v>16</v>
       </c>
       <c r="H59">
-        <v>0.34499999999999997</v>
+        <v>0.29499999999999998</v>
       </c>
       <c r="I59">
         <v>10.9</v>
       </c>
       <c r="J59">
-        <v>34.027397260273972</v>
+        <v>29.095890410958901</v>
       </c>
       <c r="K59" s="2">
-        <v>148.63638356164384</v>
+        <v>143.16734246575342</v>
       </c>
       <c r="L59" s="2">
-        <v>0.49311888888888888</v>
+        <v>0.43766888888888889</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -2809,19 +2809,19 @@
         <v>16</v>
       </c>
       <c r="H60">
-        <v>0.24</v>
+        <v>0.1825</v>
       </c>
       <c r="I60">
         <v>10.9</v>
       </c>
       <c r="J60">
-        <v>11.835616438356164</v>
+        <v>9</v>
       </c>
       <c r="K60" s="2">
-        <v>124.02569863013699</v>
+        <v>120.88100000000001</v>
       </c>
       <c r="L60" s="2">
-        <v>0.48718777777777794</v>
+        <v>0.42342027777777813</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -2847,19 +2847,19 @@
         <v>16</v>
       </c>
       <c r="H61">
-        <v>0.32500000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="I61">
         <v>10.9</v>
       </c>
       <c r="J61">
-        <v>24.041095890410961</v>
+        <v>19.972602739726032</v>
       </c>
       <c r="K61" s="2">
-        <v>137.56157534246577</v>
+        <v>133.04961643835617</v>
       </c>
       <c r="L61" s="2">
-        <v>0.50777685185185228</v>
+        <v>0.44678185185185204</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -2885,19 +2885,19 @@
         <v>16</v>
       </c>
       <c r="H62">
-        <v>0.40500000000000003</v>
+        <v>0.32750000000000001</v>
       </c>
       <c r="I62">
         <v>10.9</v>
       </c>
       <c r="J62">
-        <v>39.945205479452056</v>
+        <v>32.301369863013697</v>
       </c>
       <c r="K62" s="2">
-        <v>155.19923287671236</v>
+        <v>146.72221917808218</v>
       </c>
       <c r="L62" s="2">
-        <v>0.55965888888888915</v>
+        <v>0.47371138888888892</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">

--- a/public/datos.xlsx
+++ b/public/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NicolasAcebo\OneDrive - LARTIRIGOYEN Y CIA. S.A\Escritorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9F2405-5A48-4255-A7CC-62A770280A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C4691A-A7BA-447F-ADA6-5327F037706D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5F5C8F4A-A9C3-4394-B81C-80D194F2AEAA}"/>
   </bookViews>
@@ -2695,19 +2695,19 @@
         <v>16</v>
       </c>
       <c r="H57">
-        <v>0.155</v>
+        <v>0.19</v>
       </c>
       <c r="I57">
         <v>10.9</v>
       </c>
       <c r="J57">
-        <v>7.6438356164383565</v>
+        <v>9.3698630136986303</v>
       </c>
       <c r="K57" s="2">
-        <v>119.37701369863014</v>
+        <v>121.29117808219178</v>
       </c>
       <c r="L57" s="2">
-        <v>0.39292277777777784</v>
+        <v>0.43173777777777783</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -2733,19 +2733,19 @@
         <v>16</v>
       </c>
       <c r="H58">
-        <v>0.24</v>
+        <v>0.27250000000000002</v>
       </c>
       <c r="I58">
         <v>10.9</v>
       </c>
       <c r="J58">
-        <v>17.753424657534246</v>
+        <v>20.157534246575342</v>
       </c>
       <c r="K58" s="2">
-        <v>130.58854794520548</v>
+        <v>133.25470547945204</v>
       </c>
       <c r="L58" s="2">
-        <v>0.41351185185185169</v>
+        <v>0.44955435185185166</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -2771,19 +2771,19 @@
         <v>16</v>
       </c>
       <c r="H59">
-        <v>0.29499999999999998</v>
+        <v>0.32750000000000001</v>
       </c>
       <c r="I59">
         <v>10.9</v>
       </c>
       <c r="J59">
-        <v>29.095890410958901</v>
+        <v>32.301369863013697</v>
       </c>
       <c r="K59" s="2">
-        <v>143.16734246575342</v>
+        <v>146.72221917808218</v>
       </c>
       <c r="L59" s="2">
-        <v>0.43766888888888889</v>
+        <v>0.47371138888888892</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -2809,19 +2809,19 @@
         <v>16</v>
       </c>
       <c r="H60">
-        <v>0.1825</v>
+        <v>0.2225</v>
       </c>
       <c r="I60">
         <v>10.9</v>
       </c>
       <c r="J60">
-        <v>9</v>
+        <v>10.972602739726026</v>
       </c>
       <c r="K60" s="2">
-        <v>120.88100000000001</v>
+        <v>123.06861643835616</v>
       </c>
       <c r="L60" s="2">
-        <v>0.42342027777777813</v>
+        <v>0.4677802777777777</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -2847,19 +2847,19 @@
         <v>16</v>
       </c>
       <c r="H61">
-        <v>0.27</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="I61">
         <v>10.9</v>
       </c>
       <c r="J61">
-        <v>19.972602739726032</v>
+        <v>22.561643835616437</v>
       </c>
       <c r="K61" s="2">
-        <v>133.04961643835617</v>
+        <v>135.92086301369864</v>
       </c>
       <c r="L61" s="2">
-        <v>0.44678185185185204</v>
+        <v>0.48559685185185192</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -2885,19 +2885,19 @@
         <v>16</v>
       </c>
       <c r="H62">
-        <v>0.32750000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="I62">
         <v>10.9</v>
       </c>
       <c r="J62">
-        <v>32.301369863013697</v>
+        <v>35.506849315068493</v>
       </c>
       <c r="K62" s="2">
-        <v>146.72221917808218</v>
+        <v>150.27709589041098</v>
       </c>
       <c r="L62" s="2">
-        <v>0.47371138888888892</v>
+        <v>0.50975388888888917</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
